--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18194" uniqueCount="1484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18493" uniqueCount="1501">
   <si>
     <t>Property</t>
   </si>
@@ -1788,7 +1788,7 @@
     <t>Tillgängliggörande ändpunkt</t>
   </si>
   <si>
-    <t>2026-09-10T07:38:29+00:00</t>
+    <t>2026-10-19T12:45:34+00:00</t>
   </si>
   <si>
     <t>Den ändpunkt (TKEndpoint) som tillgängliggör denna API-instans ("tillgängliggör"). Basresursen CapabilityStatement har inget element för detta.</t>
@@ -3365,6 +3365,9 @@
   </si>
   <si>
     <t>Specifikationens kanoniska URL</t>
+  </si>
+  <si>
+    <t>Specifikationens version. url + version är unik i katalogen</t>
   </si>
   <si>
     <t>Maskinläsbart namn</t>
@@ -3992,7 +3995,7 @@
     <t>Organization.identifier</t>
   </si>
   <si>
-    <t>Organisationsidentifierare ("logisk adress"), inklusive organisationsnummer</t>
+    <t>Organisationsidentifierare ("logisk adress"): HSA-id (primär) och organisationsnummer</t>
   </si>
   <si>
     <t>Identifier for the organization that is used to identify the organization across multiple disparate systems.</t>
@@ -4005,67 +4008,117 @@
 </t>
   </si>
   <si>
+    <t>Organization.identifier:hsaId</t>
+  </si>
+  <si>
+    <t>hsaId</t>
+  </si>
+  <si>
+    <t>HSA-id (primär identifierare och logisk adress)</t>
+  </si>
+  <si>
+    <t>Organisationens HSA-id. Består av prefixet `SE`, organisationsnumret för den direktanslutna producenten i formatet tio siffror utan bindestreck, samt ett bindestreck och en efterföljande identifierande del. Organisationsnumret i HSA-id:t behöver inte vara organisationsnumret för den organisatoriska enhet som HSA-id:t identifierar. Värdet lagras, returneras och söks exakt som det är skrivet.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+tk-org-hsaid-format:HSA-id består av SE, tio siffror (den direktanslutna producentens organisationsnummer utan bindestreck), ett bindestreck och en efterföljande identifierande del. {value.matches('^SE[0-9]{10}-.+$')}</t>
+  </si>
+  <si>
+    <t>Organization.identifier:hsaId.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier:hsaId.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:hsaId.use</t>
+  </si>
+  <si>
+    <t>Organization.identifier.use</t>
+  </si>
+  <si>
+    <t>Organization.identifier:hsaId.type</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type</t>
+  </si>
+  <si>
+    <t>Organization.identifier:hsaId.system</t>
+  </si>
+  <si>
+    <t>Organization.identifier.system</t>
+  </si>
+  <si>
+    <t>urn:oid:1.2.752.29.4.19</t>
+  </si>
+  <si>
+    <t>Organization.identifier:hsaId.value</t>
+  </si>
+  <si>
+    <t>Organization.identifier.value</t>
+  </si>
+  <si>
+    <t>HSA-id, t.ex. SE2321000016-1003</t>
+  </si>
+  <si>
+    <t>Organization.identifier:hsaId.period</t>
+  </si>
+  <si>
+    <t>Organization.identifier.period</t>
+  </si>
+  <si>
+    <t>Organization.identifier:hsaId.assigner</t>
+  </si>
+  <si>
+    <t>Organization.identifier.assigner</t>
+  </si>
+  <si>
     <t>Organization.identifier:organisationsnummer</t>
   </si>
   <si>
     <t>organisationsnummer</t>
   </si>
   <si>
-    <t>Identifies this organization  across multiple systems</t>
+    <t>Organisationsnummer (anges bara på den juridiska personen)</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+tk-org-orgnr-format:Organisationsnummer anges som tio siffror utan bindestreck. {value.matches('^[0-9]{10}$')}</t>
   </si>
   <si>
     <t>Organization.identifier:organisationsnummer.id</t>
   </si>
   <si>
-    <t>Organization.identifier.id</t>
-  </si>
-  <si>
     <t>Organization.identifier:organisationsnummer.extension</t>
   </si>
   <si>
-    <t>Organization.identifier.extension</t>
-  </si>
-  <si>
     <t>Organization.identifier:organisationsnummer.use</t>
   </si>
   <si>
-    <t>Organization.identifier.use</t>
-  </si>
-  <si>
     <t>Organization.identifier:organisationsnummer.type</t>
   </si>
   <si>
-    <t>Organization.identifier.type</t>
-  </si>
-  <si>
     <t>Organization.identifier:organisationsnummer.system</t>
   </si>
   <si>
-    <t>Organization.identifier.system</t>
-  </si>
-  <si>
     <t>urn:oid:2.5.4.97</t>
   </si>
   <si>
     <t>Organization.identifier:organisationsnummer.value</t>
   </si>
   <si>
-    <t>Organization.identifier.value</t>
-  </si>
-  <si>
-    <t>Svenskt organisationsnummer</t>
+    <t>Svenskt organisationsnummer, 10 siffror utan bindestreck (t.ex. 2321000016)</t>
   </si>
   <si>
     <t>Organization.identifier:organisationsnummer.period</t>
   </si>
   <si>
-    <t>Organization.identifier.period</t>
-  </si>
-  <si>
     <t>Organization.identifier:organisationsnummer.assigner</t>
-  </si>
-  <si>
-    <t>Organization.identifier.assigner</t>
   </si>
   <si>
     <t>Organization.active</t>
@@ -4172,7 +4225,7 @@
     <t>Organization.partOf</t>
   </si>
   <si>
-    <t>The organization of which this organization forms a part</t>
+    <t>Överordnad organisation, t.ex. vårdgivaren för en vårdenhet</t>
   </si>
   <si>
     <t>The organization of which this organization forms a part.</t>
@@ -5837,7 +5890,7 @@
         <v>2</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>1080</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="135">
@@ -5845,7 +5898,7 @@
         <v>4</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>1081</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="136">
@@ -5861,7 +5914,7 @@
         <v>9</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>1082</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="138">
@@ -6007,7 +6060,7 @@
         <v>2</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>1083</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="157">
@@ -6015,7 +6068,7 @@
         <v>4</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>1084</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="158">
@@ -6031,7 +6084,7 @@
         <v>9</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>1085</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="160">
@@ -6177,7 +6230,7 @@
         <v>2</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>1086</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="179">
@@ -6185,7 +6238,7 @@
         <v>4</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>1087</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="180">
@@ -6201,7 +6254,7 @@
         <v>9</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>1088</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="182">
@@ -6347,7 +6400,7 @@
         <v>2</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>1089</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="201">
@@ -6355,7 +6408,7 @@
         <v>4</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>1090</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="202">
@@ -6371,7 +6424,7 @@
         <v>9</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>1091</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="204">
@@ -6379,7 +6432,7 @@
         <v>10</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>1092</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="205">
@@ -6433,7 +6486,7 @@
         <v>23</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>1093</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="212">
@@ -6501,7 +6554,7 @@
         <v>569</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>1094</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="221">
@@ -6517,7 +6570,7 @@
         <v>2</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>1095</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="223">
@@ -6525,7 +6578,7 @@
         <v>4</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>1096</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="224">
@@ -6541,7 +6594,7 @@
         <v>9</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>1097</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="226">
@@ -6549,7 +6602,7 @@
         <v>10</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>1098</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="227">
@@ -6603,7 +6656,7 @@
         <v>23</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="234">
@@ -6671,7 +6724,7 @@
         <v>569</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>1100</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="243">
@@ -6687,7 +6740,7 @@
         <v>2</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="245">
@@ -6695,7 +6748,7 @@
         <v>4</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="246">
@@ -6711,7 +6764,7 @@
         <v>9</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="248">
@@ -6719,7 +6772,7 @@
         <v>10</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>1106</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="249">
@@ -6773,7 +6826,7 @@
         <v>23</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="256">
@@ -6841,7 +6894,7 @@
         <v>569</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>1094</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="265">
@@ -6857,7 +6910,7 @@
         <v>2</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="267">
@@ -6865,7 +6918,7 @@
         <v>4</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>1110</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="268">
@@ -6873,7 +6926,7 @@
         <v>6</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>1111</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="269">
@@ -6889,7 +6942,7 @@
         <v>9</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>1111</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="271">
@@ -6897,7 +6950,7 @@
         <v>10</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>1112</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="272">
@@ -6951,7 +7004,7 @@
         <v>23</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>1113</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="279">
@@ -6987,7 +7040,7 @@
         <v>31</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>1114</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="284">
@@ -6995,7 +7048,7 @@
         <v>33</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>1115</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="285">
@@ -7027,7 +7080,7 @@
         <v>2</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>1229</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="289">
@@ -7035,7 +7088,7 @@
         <v>4</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>1230</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="290">
@@ -7051,7 +7104,7 @@
         <v>9</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>1231</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="292">
@@ -7059,7 +7112,7 @@
         <v>10</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>1232</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="293">
@@ -7113,7 +7166,7 @@
         <v>23</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>1233</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="300">
@@ -7141,7 +7194,7 @@
         <v>29</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>1234</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="304">
@@ -7149,7 +7202,7 @@
         <v>31</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>1230</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="305">
@@ -7157,7 +7210,7 @@
         <v>33</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>1235</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="306">
@@ -7173,7 +7226,7 @@
         <v>37</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>1236</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="308">
@@ -7189,7 +7242,7 @@
         <v>2</v>
       </c>
       <c r="B309" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="310">
@@ -7197,7 +7250,7 @@
         <v>4</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>1250</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="311">
@@ -7205,7 +7258,7 @@
         <v>6</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>1251</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="312">
@@ -7221,7 +7274,7 @@
         <v>9</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>1251</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="314">
@@ -7229,7 +7282,7 @@
         <v>10</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>1252</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="315">
@@ -7283,7 +7336,7 @@
         <v>23</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>1253</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="322">
@@ -7319,7 +7372,7 @@
         <v>31</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="327">
@@ -7327,7 +7380,7 @@
         <v>33</v>
       </c>
       <c r="B327" t="s" s="2">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="328">
@@ -7359,7 +7412,7 @@
         <v>2</v>
       </c>
       <c r="B331" t="s" s="2">
-        <v>1354</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="332">
@@ -7367,7 +7420,7 @@
         <v>4</v>
       </c>
       <c r="B332" t="s" s="2">
-        <v>1355</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="333">
@@ -7375,7 +7428,7 @@
         <v>6</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>1356</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="334">
@@ -7391,7 +7444,7 @@
         <v>9</v>
       </c>
       <c r="B335" t="s" s="2">
-        <v>1356</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="336">
@@ -7399,7 +7452,7 @@
         <v>10</v>
       </c>
       <c r="B336" t="s" s="2">
-        <v>1357</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="337">
@@ -7453,7 +7506,7 @@
         <v>23</v>
       </c>
       <c r="B343" t="s" s="2">
-        <v>1358</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="344">
@@ -7489,7 +7542,7 @@
         <v>31</v>
       </c>
       <c r="B348" t="s" s="2">
-        <v>1359</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="349">
@@ -7497,7 +7550,7 @@
         <v>33</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>1360</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="350">
@@ -7529,7 +7582,7 @@
         <v>2</v>
       </c>
       <c r="B353" t="s" s="2">
-        <v>1476</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="354">
@@ -7537,7 +7590,7 @@
         <v>4</v>
       </c>
       <c r="B354" t="s" s="2">
-        <v>1477</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="355">
@@ -7553,7 +7606,7 @@
         <v>9</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>1478</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="357">
@@ -7561,7 +7614,7 @@
         <v>10</v>
       </c>
       <c r="B357" t="s" s="2">
-        <v>1479</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="358">
@@ -7615,7 +7668,7 @@
         <v>23</v>
       </c>
       <c r="B364" t="s" s="2">
-        <v>1480</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="365">
@@ -7643,7 +7696,7 @@
         <v>29</v>
       </c>
       <c r="B368" t="s" s="2">
-        <v>1234</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="369">
@@ -7651,7 +7704,7 @@
         <v>31</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>1477</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="370">
@@ -7659,7 +7712,7 @@
         <v>33</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>1235</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="371">
@@ -7675,7 +7728,7 @@
         <v>37</v>
       </c>
       <c r="B372" t="s" s="2">
-        <v>1236</v>
+        <v>1237</v>
       </c>
     </row>
   </sheetData>
@@ -7685,7 +7738,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK532"/>
+  <dimension ref="A1:AK541"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="38.703125" customWidth="true" bestFit="true"/>
@@ -35003,7 +35056,7 @@
       </c>
       <c r="F261" s="2"/>
       <c r="G261" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H261" t="s" s="2">
         <v>84</v>
@@ -35021,7 +35074,7 @@
         <v>194</v>
       </c>
       <c r="M261" t="s" s="2">
-        <v>625</v>
+        <v>1069</v>
       </c>
       <c r="N261" t="s" s="2">
         <v>626</v>
@@ -35229,7 +35282,7 @@
         <v>194</v>
       </c>
       <c r="M263" t="s" s="2">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="N263" t="s" s="2">
         <v>636</v>
@@ -35336,7 +35389,7 @@
         <v>194</v>
       </c>
       <c r="M264" t="s" s="2">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="N264" t="s" s="2">
         <v>642</v>
@@ -35655,7 +35708,7 @@
         <v>658</v>
       </c>
       <c r="M267" t="s" s="2">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="N267" t="s" s="2">
         <v>660</v>
@@ -35972,7 +36025,7 @@
         <v>673</v>
       </c>
       <c r="M270" t="s" s="2">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="N270" t="s" s="2">
         <v>675</v>
@@ -36608,7 +36661,7 @@
         <v>104</v>
       </c>
       <c r="M276" t="s" s="2">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="N276" t="s" s="2">
         <v>707</v>
@@ -36625,7 +36678,7 @@
         <v>78</v>
       </c>
       <c r="T276" t="s" s="2">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="U276" t="s" s="2">
         <v>78</v>
@@ -36713,7 +36766,7 @@
         <v>714</v>
       </c>
       <c r="M277" t="s" s="2">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="N277" t="s" s="2">
         <v>716</v>
@@ -38070,7 +38123,7 @@
         <v>673</v>
       </c>
       <c r="M290" t="s" s="2">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="N290" t="s" s="2">
         <v>748</v>
@@ -38173,7 +38226,7 @@
         <v>750</v>
       </c>
       <c r="M291" t="s" s="2">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="N291" t="s" s="2">
         <v>752</v>
@@ -38276,7 +38329,7 @@
         <v>209</v>
       </c>
       <c r="M292" t="s" s="2">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="N292" t="s" s="2">
         <v>755</v>
@@ -39427,7 +39480,7 @@
         <v>673</v>
       </c>
       <c r="M303" t="s" s="2">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="N303" t="s" s="2">
         <v>800</v>
@@ -47961,7 +48014,7 @@
     </row>
     <row r="385">
       <c r="A385" t="s" s="2">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B385" t="s" s="2">
         <v>567</v>
@@ -48064,7 +48117,7 @@
     </row>
     <row r="386">
       <c r="A386" t="s" s="2">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B386" t="s" s="2">
         <v>571</v>
@@ -48167,7 +48220,7 @@
     </row>
     <row r="387">
       <c r="A387" t="s" s="2">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B387" t="s" s="2">
         <v>572</v>
@@ -48270,7 +48323,7 @@
     </row>
     <row r="388">
       <c r="A388" t="s" s="2">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B388" t="s" s="2">
         <v>574</v>
@@ -48316,7 +48369,7 @@
       </c>
       <c r="R388" s="2"/>
       <c r="S388" t="s" s="2">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="T388" t="s" s="2">
         <v>78</v>
@@ -48375,7 +48428,7 @@
     </row>
     <row r="389">
       <c r="A389" t="s" s="2">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B389" t="s" s="2">
         <v>578</v>
@@ -48478,7 +48531,7 @@
     </row>
     <row r="390">
       <c r="A390" t="s" s="2">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B390" t="s" s="2">
         <v>567</v>
@@ -48581,7 +48634,7 @@
     </row>
     <row r="391">
       <c r="A391" t="s" s="2">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B391" t="s" s="2">
         <v>571</v>
@@ -48684,7 +48737,7 @@
     </row>
     <row r="392">
       <c r="A392" t="s" s="2">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B392" t="s" s="2">
         <v>572</v>
@@ -48787,7 +48840,7 @@
     </row>
     <row r="393">
       <c r="A393" t="s" s="2">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B393" t="s" s="2">
         <v>574</v>
@@ -48833,7 +48886,7 @@
       </c>
       <c r="R393" s="2"/>
       <c r="S393" t="s" s="2">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="T393" t="s" s="2">
         <v>78</v>
@@ -48892,7 +48945,7 @@
     </row>
     <row r="394">
       <c r="A394" t="s" s="2">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B394" t="s" s="2">
         <v>578</v>
@@ -48995,7 +49048,7 @@
     </row>
     <row r="395">
       <c r="A395" t="s" s="2">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B395" t="s" s="2">
         <v>567</v>
@@ -49098,7 +49151,7 @@
     </row>
     <row r="396">
       <c r="A396" t="s" s="2">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B396" t="s" s="2">
         <v>571</v>
@@ -49201,7 +49254,7 @@
     </row>
     <row r="397">
       <c r="A397" t="s" s="2">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B397" t="s" s="2">
         <v>572</v>
@@ -49304,7 +49357,7 @@
     </row>
     <row r="398">
       <c r="A398" t="s" s="2">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B398" t="s" s="2">
         <v>574</v>
@@ -49350,7 +49403,7 @@
       </c>
       <c r="R398" s="2"/>
       <c r="S398" t="s" s="2">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="T398" t="s" s="2">
         <v>78</v>
@@ -49409,7 +49462,7 @@
     </row>
     <row r="399">
       <c r="A399" t="s" s="2">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B399" t="s" s="2">
         <v>578</v>
@@ -49512,7 +49565,7 @@
     </row>
     <row r="400">
       <c r="A400" t="s" s="2">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B400" t="s" s="2">
         <v>567</v>
@@ -49544,10 +49597,10 @@
         <v>79</v>
       </c>
       <c r="M400" t="s" s="2">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="N400" t="s" s="2">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="O400" s="2"/>
       <c r="P400" s="2"/>
@@ -49615,7 +49668,7 @@
     </row>
     <row r="401">
       <c r="A401" t="s" s="2">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B401" t="s" s="2">
         <v>571</v>
@@ -49718,7 +49771,7 @@
     </row>
     <row r="402">
       <c r="A402" t="s" s="2">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B402" t="s" s="2">
         <v>572</v>
@@ -49821,7 +49874,7 @@
     </row>
     <row r="403">
       <c r="A403" t="s" s="2">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B403" t="s" s="2">
         <v>574</v>
@@ -49867,7 +49920,7 @@
       </c>
       <c r="R403" s="2"/>
       <c r="S403" t="s" s="2">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="T403" t="s" s="2">
         <v>78</v>
@@ -49926,7 +49979,7 @@
     </row>
     <row r="404">
       <c r="A404" t="s" s="2">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B404" t="s" s="2">
         <v>578</v>
@@ -50029,7 +50082,7 @@
     </row>
     <row r="405">
       <c r="A405" t="s" s="2">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B405" t="s" s="2">
         <v>567</v>
@@ -50061,10 +50114,10 @@
         <v>79</v>
       </c>
       <c r="M405" t="s" s="2">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="N405" t="s" s="2">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="O405" s="2"/>
       <c r="P405" s="2"/>
@@ -50132,7 +50185,7 @@
     </row>
     <row r="406">
       <c r="A406" t="s" s="2">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B406" t="s" s="2">
         <v>571</v>
@@ -50235,7 +50288,7 @@
     </row>
     <row r="407">
       <c r="A407" t="s" s="2">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B407" t="s" s="2">
         <v>572</v>
@@ -50338,7 +50391,7 @@
     </row>
     <row r="408">
       <c r="A408" t="s" s="2">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B408" t="s" s="2">
         <v>574</v>
@@ -50384,7 +50437,7 @@
       </c>
       <c r="R408" s="2"/>
       <c r="S408" t="s" s="2">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="T408" t="s" s="2">
         <v>78</v>
@@ -50443,7 +50496,7 @@
     </row>
     <row r="409">
       <c r="A409" t="s" s="2">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B409" t="s" s="2">
         <v>578</v>
@@ -50472,10 +50525,10 @@
         <v>78</v>
       </c>
       <c r="L409" t="s" s="2">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="M409" t="s" s="2">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="N409" t="s" s="2">
         <v>581</v>
@@ -50546,7 +50599,7 @@
     </row>
     <row r="410">
       <c r="A410" t="s" s="2">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B410" t="s" s="2">
         <v>567</v>
@@ -50578,10 +50631,10 @@
         <v>79</v>
       </c>
       <c r="M410" t="s" s="2">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="N410" t="s" s="2">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="O410" s="2"/>
       <c r="P410" s="2"/>
@@ -50649,7 +50702,7 @@
     </row>
     <row r="411">
       <c r="A411" t="s" s="2">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B411" t="s" s="2">
         <v>571</v>
@@ -50752,7 +50805,7 @@
     </row>
     <row r="412">
       <c r="A412" t="s" s="2">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B412" t="s" s="2">
         <v>572</v>
@@ -50855,7 +50908,7 @@
     </row>
     <row r="413">
       <c r="A413" t="s" s="2">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B413" t="s" s="2">
         <v>574</v>
@@ -50901,7 +50954,7 @@
       </c>
       <c r="R413" s="2"/>
       <c r="S413" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="T413" t="s" s="2">
         <v>78</v>
@@ -50960,7 +51013,7 @@
     </row>
     <row r="414">
       <c r="A414" t="s" s="2">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B414" t="s" s="2">
         <v>578</v>
@@ -51026,7 +51079,7 @@
       </c>
       <c r="Z414" s="2"/>
       <c r="AA414" t="s" s="2">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="AB414" t="s" s="2">
         <v>78</v>
@@ -51061,13 +51114,13 @@
     </row>
     <row r="415">
       <c r="A415" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B415" t="s" s="2">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="C415" t="s" s="2">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D415" s="2"/>
       <c r="E415" t="s" s="2">
@@ -51093,10 +51146,10 @@
         <v>79</v>
       </c>
       <c r="M415" t="s" s="2">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="N415" t="s" s="2">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="O415" s="2"/>
       <c r="P415" s="2"/>
@@ -51147,7 +51200,7 @@
         <v>78</v>
       </c>
       <c r="AG415" t="s" s="2">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="AH415" t="s" s="2">
         <v>76</v>
@@ -51164,13 +51217,13 @@
     </row>
     <row r="416">
       <c r="A416" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B416" t="s" s="2">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="C416" t="s" s="2">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="D416" s="2"/>
       <c r="E416" t="s" s="2">
@@ -51269,13 +51322,13 @@
     </row>
     <row r="417">
       <c r="A417" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="C417" t="s" s="2">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="D417" s="2"/>
       <c r="E417" t="s" s="2">
@@ -51372,13 +51425,13 @@
     </row>
     <row r="418">
       <c r="A418" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B418" t="s" s="2">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="C418" t="s" s="2">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="D418" s="2"/>
       <c r="E418" t="s" s="2">
@@ -51477,13 +51530,13 @@
     </row>
     <row r="419">
       <c r="A419" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B419" t="s" s="2">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="C419" t="s" s="2">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D419" s="2"/>
       <c r="E419" t="s" s="2">
@@ -51582,13 +51635,13 @@
     </row>
     <row r="420">
       <c r="A420" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B420" t="s" s="2">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="C420" t="s" s="2">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="D420" s="2"/>
       <c r="E420" t="s" s="2">
@@ -51687,13 +51740,13 @@
     </row>
     <row r="421">
       <c r="A421" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B421" t="s" s="2">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="C421" t="s" s="2">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="D421" s="2"/>
       <c r="E421" t="s" s="2">
@@ -51792,13 +51845,13 @@
     </row>
     <row r="422">
       <c r="A422" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="C422" t="s" s="2">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="D422" s="2"/>
       <c r="E422" t="s" s="2">
@@ -51893,16 +51946,16 @@
     </row>
     <row r="423">
       <c r="A423" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B423" t="s" s="2">
+        <v>1126</v>
+      </c>
+      <c r="C423" t="s" s="2">
         <v>1125</v>
       </c>
-      <c r="C423" t="s" s="2">
-        <v>1124</v>
-      </c>
       <c r="D423" t="s" s="2">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="E423" t="s" s="2">
         <v>78</v>
@@ -51924,13 +51977,13 @@
         <v>78</v>
       </c>
       <c r="L423" t="s" s="2">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="M423" t="s" s="2">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="N423" t="s" s="2">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="O423" s="2"/>
       <c r="P423" s="2"/>
@@ -51998,16 +52051,16 @@
     </row>
     <row r="424">
       <c r="A424" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B424" t="s" s="2">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="C424" t="s" s="2">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="D424" t="s" s="2">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="E424" t="s" s="2">
         <v>78</v>
@@ -52029,13 +52082,13 @@
         <v>78</v>
       </c>
       <c r="L424" t="s" s="2">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="M424" t="s" s="2">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="N424" t="s" s="2">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="O424" s="2"/>
       <c r="P424" s="2"/>
@@ -52103,13 +52156,13 @@
     </row>
     <row r="425">
       <c r="A425" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B425" t="s" s="2">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="C425" t="s" s="2">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="D425" s="2"/>
       <c r="E425" t="s" s="2">
@@ -52210,13 +52263,13 @@
     </row>
     <row r="426">
       <c r="A426" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B426" t="s" s="2">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="C426" t="s" s="2">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="D426" s="2"/>
       <c r="E426" t="s" s="2">
@@ -52242,10 +52295,10 @@
         <v>142</v>
       </c>
       <c r="M426" t="s" s="2">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="N426" t="s" s="2">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="O426" s="2"/>
       <c r="P426" s="2"/>
@@ -52294,7 +52347,7 @@
         <v>147</v>
       </c>
       <c r="AG426" t="s" s="2">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="AH426" t="s" s="2">
         <v>76</v>
@@ -52311,16 +52364,16 @@
     </row>
     <row r="427">
       <c r="A427" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B427" t="s" s="2">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="C427" t="s" s="2">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="D427" t="s" s="2">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="E427" t="s" s="2">
         <v>78</v>
@@ -52345,10 +52398,10 @@
         <v>142</v>
       </c>
       <c r="M427" t="s" s="2">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="N427" t="s" s="2">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="O427" s="2"/>
       <c r="P427" s="2"/>
@@ -52399,7 +52452,7 @@
         <v>78</v>
       </c>
       <c r="AG427" t="s" s="2">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="AH427" t="s" s="2">
         <v>76</v>
@@ -52416,13 +52469,13 @@
     </row>
     <row r="428">
       <c r="A428" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B428" t="s" s="2">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C428" t="s" s="2">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D428" s="2"/>
       <c r="E428" t="s" s="2">
@@ -52519,13 +52572,13 @@
     </row>
     <row r="429">
       <c r="A429" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B429" t="s" s="2">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="C429" t="s" s="2">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="D429" s="2"/>
       <c r="E429" t="s" s="2">
@@ -52624,13 +52677,13 @@
     </row>
     <row r="430">
       <c r="A430" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B430" t="s" s="2">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="C430" t="s" s="2">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="D430" s="2"/>
       <c r="E430" t="s" s="2">
@@ -52731,13 +52784,13 @@
     </row>
     <row r="431">
       <c r="A431" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B431" t="s" s="2">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="C431" t="s" s="2">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="D431" s="2"/>
       <c r="E431" t="s" s="2">
@@ -52838,13 +52891,13 @@
     </row>
     <row r="432">
       <c r="A432" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B432" t="s" s="2">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="C432" t="s" s="2">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="D432" s="2"/>
       <c r="E432" t="s" s="2">
@@ -52889,7 +52942,7 @@
         <v>78</v>
       </c>
       <c r="T432" t="s" s="2">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="U432" t="s" s="2">
         <v>190</v>
@@ -52945,13 +52998,13 @@
     </row>
     <row r="433">
       <c r="A433" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B433" t="s" s="2">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="C433" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="D433" s="2"/>
       <c r="E433" t="s" s="2">
@@ -52977,7 +53030,7 @@
         <v>194</v>
       </c>
       <c r="M433" t="s" s="2">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="N433" t="s" s="2">
         <v>196</v>
@@ -53050,13 +53103,13 @@
     </row>
     <row r="434">
       <c r="A434" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B434" t="s" s="2">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="C434" t="s" s="2">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="D434" s="2"/>
       <c r="E434" t="s" s="2">
@@ -53153,13 +53206,13 @@
     </row>
     <row r="435">
       <c r="A435" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B435" t="s" s="2">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="C435" t="s" s="2">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="D435" s="2"/>
       <c r="E435" t="s" s="2">
@@ -53258,13 +53311,13 @@
     </row>
     <row r="436">
       <c r="A436" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B436" t="s" s="2">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="C436" t="s" s="2">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="D436" s="2"/>
       <c r="E436" t="s" s="2">
@@ -53290,13 +53343,13 @@
         <v>104</v>
       </c>
       <c r="M436" t="s" s="2">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="N436" t="s" s="2">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="O436" t="s" s="2">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="P436" s="2"/>
       <c r="Q436" t="s" s="2">
@@ -53325,10 +53378,10 @@
         <v>108</v>
       </c>
       <c r="Z436" t="s" s="2">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="AA436" t="s" s="2">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="AB436" t="s" s="2">
         <v>78</v>
@@ -53346,7 +53399,7 @@
         <v>78</v>
       </c>
       <c r="AG436" t="s" s="2">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="AH436" t="s" s="2">
         <v>84</v>
@@ -53363,13 +53416,13 @@
     </row>
     <row r="437">
       <c r="A437" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B437" t="s" s="2">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="C437" t="s" s="2">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="D437" s="2"/>
       <c r="E437" t="s" s="2">
@@ -53395,13 +53448,13 @@
         <v>174</v>
       </c>
       <c r="M437" t="s" s="2">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="N437" t="s" s="2">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="O437" t="s" s="2">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="P437" s="2"/>
       <c r="Q437" t="s" s="2">
@@ -53431,7 +53484,7 @@
       </c>
       <c r="Z437" s="2"/>
       <c r="AA437" t="s" s="2">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="AB437" t="s" s="2">
         <v>78</v>
@@ -53449,7 +53502,7 @@
         <v>78</v>
       </c>
       <c r="AG437" t="s" s="2">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="AH437" t="s" s="2">
         <v>84</v>
@@ -53466,13 +53519,13 @@
     </row>
     <row r="438">
       <c r="A438" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B438" t="s" s="2">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="C438" t="s" s="2">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="D438" s="2"/>
       <c r="E438" t="s" s="2">
@@ -53498,10 +53551,10 @@
         <v>194</v>
       </c>
       <c r="M438" t="s" s="2">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="N438" t="s" s="2">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="O438" s="2"/>
       <c r="P438" s="2"/>
@@ -53552,7 +53605,7 @@
         <v>78</v>
       </c>
       <c r="AG438" t="s" s="2">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="AH438" t="s" s="2">
         <v>76</v>
@@ -53569,13 +53622,13 @@
     </row>
     <row r="439">
       <c r="A439" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B439" t="s" s="2">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="C439" t="s" s="2">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="D439" s="2"/>
       <c r="E439" t="s" s="2">
@@ -53601,10 +53654,10 @@
         <v>194</v>
       </c>
       <c r="M439" t="s" s="2">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="N439" t="s" s="2">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="O439" s="2"/>
       <c r="P439" s="2"/>
@@ -53655,7 +53708,7 @@
         <v>78</v>
       </c>
       <c r="AG439" t="s" s="2">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="AH439" t="s" s="2">
         <v>76</v>
@@ -53672,13 +53725,13 @@
     </row>
     <row r="440">
       <c r="A440" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B440" t="s" s="2">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="C440" t="s" s="2">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="D440" s="2"/>
       <c r="E440" t="s" s="2">
@@ -53704,10 +53757,10 @@
         <v>174</v>
       </c>
       <c r="M440" t="s" s="2">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="N440" t="s" s="2">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="O440" s="2"/>
       <c r="P440" s="2"/>
@@ -53738,7 +53791,7 @@
       </c>
       <c r="Z440" s="2"/>
       <c r="AA440" t="s" s="2">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="AB440" t="s" s="2">
         <v>78</v>
@@ -53756,7 +53809,7 @@
         <v>78</v>
       </c>
       <c r="AG440" t="s" s="2">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="AH440" t="s" s="2">
         <v>76</v>
@@ -53773,13 +53826,13 @@
     </row>
     <row r="441">
       <c r="A441" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B441" t="s" s="2">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="C441" t="s" s="2">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="D441" s="2"/>
       <c r="E441" t="s" s="2">
@@ -53805,13 +53858,13 @@
         <v>509</v>
       </c>
       <c r="M441" t="s" s="2">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="N441" t="s" s="2">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="O441" t="s" s="2">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="P441" s="2"/>
       <c r="Q441" t="s" s="2">
@@ -53861,7 +53914,7 @@
         <v>78</v>
       </c>
       <c r="AG441" t="s" s="2">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="AH441" t="s" s="2">
         <v>76</v>
@@ -53878,13 +53931,13 @@
     </row>
     <row r="442">
       <c r="A442" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B442" t="s" s="2">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="C442" t="s" s="2">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="D442" s="2"/>
       <c r="E442" t="s" s="2">
@@ -53910,10 +53963,10 @@
         <v>269</v>
       </c>
       <c r="M442" t="s" s="2">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="N442" t="s" s="2">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="O442" s="2"/>
       <c r="P442" s="2"/>
@@ -53964,7 +54017,7 @@
         <v>78</v>
       </c>
       <c r="AG442" t="s" s="2">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="AH442" t="s" s="2">
         <v>76</v>
@@ -53981,13 +54034,13 @@
     </row>
     <row r="443">
       <c r="A443" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B443" t="s" s="2">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C443" t="s" s="2">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="D443" s="2"/>
       <c r="E443" t="s" s="2">
@@ -54013,13 +54066,13 @@
         <v>203</v>
       </c>
       <c r="M443" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="N443" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="O443" t="s" s="2">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="P443" s="2"/>
       <c r="Q443" t="s" s="2">
@@ -54069,7 +54122,7 @@
         <v>78</v>
       </c>
       <c r="AG443" t="s" s="2">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="AH443" t="s" s="2">
         <v>76</v>
@@ -54086,13 +54139,13 @@
     </row>
     <row r="444">
       <c r="A444" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B444" t="s" s="2">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="C444" t="s" s="2">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="D444" s="2"/>
       <c r="E444" t="s" s="2">
@@ -54189,13 +54242,13 @@
     </row>
     <row r="445">
       <c r="A445" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B445" t="s" s="2">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C445" t="s" s="2">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="D445" s="2"/>
       <c r="E445" t="s" s="2">
@@ -54294,13 +54347,13 @@
     </row>
     <row r="446">
       <c r="A446" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B446" t="s" s="2">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="C446" t="s" s="2">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="D446" s="2"/>
       <c r="E446" t="s" s="2">
@@ -54326,13 +54379,13 @@
         <v>658</v>
       </c>
       <c r="M446" t="s" s="2">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="N446" t="s" s="2">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="O446" t="s" s="2">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="P446" s="2"/>
       <c r="Q446" t="s" s="2">
@@ -54382,7 +54435,7 @@
         <v>78</v>
       </c>
       <c r="AG446" t="s" s="2">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="AH446" t="s" s="2">
         <v>76</v>
@@ -54391,7 +54444,7 @@
         <v>84</v>
       </c>
       <c r="AJ446" t="s" s="2">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="AK446" t="s" s="2">
         <v>96</v>
@@ -54399,13 +54452,13 @@
     </row>
     <row r="447">
       <c r="A447" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B447" t="s" s="2">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="C447" t="s" s="2">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="D447" s="2"/>
       <c r="E447" t="s" s="2">
@@ -54431,20 +54484,20 @@
         <v>658</v>
       </c>
       <c r="M447" t="s" s="2">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="N447" t="s" s="2">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="O447" t="s" s="2">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="P447" s="2"/>
       <c r="Q447" t="s" s="2">
         <v>78</v>
       </c>
       <c r="R447" t="s" s="2">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="S447" t="s" s="2">
         <v>78</v>
@@ -54489,7 +54542,7 @@
         <v>78</v>
       </c>
       <c r="AG447" t="s" s="2">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="AH447" t="s" s="2">
         <v>76</v>
@@ -54498,7 +54551,7 @@
         <v>84</v>
       </c>
       <c r="AJ447" t="s" s="2">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="AK447" t="s" s="2">
         <v>96</v>
@@ -54506,13 +54559,13 @@
     </row>
     <row r="448">
       <c r="A448" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B448" t="s" s="2">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="C448" t="s" s="2">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="D448" s="2"/>
       <c r="E448" t="s" s="2">
@@ -54538,13 +54591,13 @@
         <v>383</v>
       </c>
       <c r="M448" t="s" s="2">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="N448" t="s" s="2">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="O448" t="s" s="2">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="P448" s="2"/>
       <c r="Q448" t="s" s="2">
@@ -54594,7 +54647,7 @@
         <v>78</v>
       </c>
       <c r="AG448" t="s" s="2">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="AH448" t="s" s="2">
         <v>76</v>
@@ -54611,13 +54664,13 @@
     </row>
     <row r="449">
       <c r="A449" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B449" t="s" s="2">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="C449" t="s" s="2">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="D449" s="2"/>
       <c r="E449" t="s" s="2">
@@ -54714,13 +54767,13 @@
     </row>
     <row r="450">
       <c r="A450" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B450" t="s" s="2">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="C450" t="s" s="2">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="D450" s="2"/>
       <c r="E450" t="s" s="2">
@@ -54815,16 +54868,16 @@
     </row>
     <row r="451">
       <c r="A451" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B451" t="s" s="2">
+        <v>1209</v>
+      </c>
+      <c r="C451" t="s" s="2">
         <v>1208</v>
       </c>
-      <c r="C451" t="s" s="2">
-        <v>1207</v>
-      </c>
       <c r="D451" t="s" s="2">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="E451" t="s" s="2">
         <v>78</v>
@@ -54846,13 +54899,13 @@
         <v>78</v>
       </c>
       <c r="L451" t="s" s="2">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="M451" t="s" s="2">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="N451" t="s" s="2">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="O451" s="2"/>
       <c r="P451" s="2"/>
@@ -54920,13 +54973,13 @@
     </row>
     <row r="452">
       <c r="A452" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B452" t="s" s="2">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="C452" t="s" s="2">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="D452" s="2"/>
       <c r="E452" t="s" s="2">
@@ -55027,13 +55080,13 @@
     </row>
     <row r="453">
       <c r="A453" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B453" t="s" s="2">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="C453" t="s" s="2">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="D453" s="2"/>
       <c r="E453" t="s" s="2">
@@ -55059,13 +55112,13 @@
         <v>174</v>
       </c>
       <c r="M453" t="s" s="2">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="N453" t="s" s="2">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="O453" t="s" s="2">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="P453" s="2"/>
       <c r="Q453" t="s" s="2">
@@ -55095,7 +55148,7 @@
       </c>
       <c r="Z453" s="2"/>
       <c r="AA453" t="s" s="2">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="AB453" t="s" s="2">
         <v>78</v>
@@ -55113,7 +55166,7 @@
         <v>78</v>
       </c>
       <c r="AG453" t="s" s="2">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="AH453" t="s" s="2">
         <v>76</v>
@@ -55130,13 +55183,13 @@
     </row>
     <row r="454">
       <c r="A454" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B454" t="s" s="2">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="C454" t="s" s="2">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="D454" s="2"/>
       <c r="E454" t="s" s="2">
@@ -55162,13 +55215,13 @@
         <v>104</v>
       </c>
       <c r="M454" t="s" s="2">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="N454" t="s" s="2">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="O454" t="s" s="2">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="P454" s="2"/>
       <c r="Q454" t="s" s="2">
@@ -55218,7 +55271,7 @@
         <v>78</v>
       </c>
       <c r="AG454" t="s" s="2">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="AH454" t="s" s="2">
         <v>76</v>
@@ -55235,13 +55288,13 @@
     </row>
     <row r="455">
       <c r="A455" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B455" t="s" s="2">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="C455" t="s" s="2">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="D455" s="2"/>
       <c r="E455" t="s" s="2">
@@ -55267,13 +55320,13 @@
         <v>750</v>
       </c>
       <c r="M455" t="s" s="2">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="N455" t="s" s="2">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="O455" t="s" s="2">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="P455" s="2"/>
       <c r="Q455" t="s" s="2">
@@ -55323,7 +55376,7 @@
         <v>78</v>
       </c>
       <c r="AG455" t="s" s="2">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="AH455" t="s" s="2">
         <v>84</v>
@@ -55340,13 +55393,13 @@
     </row>
     <row r="456">
       <c r="A456" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B456" t="s" s="2">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="C456" t="s" s="2">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="D456" s="2"/>
       <c r="E456" t="s" s="2">
@@ -55372,13 +55425,13 @@
         <v>194</v>
       </c>
       <c r="M456" t="s" s="2">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="N456" t="s" s="2">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="O456" t="s" s="2">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="P456" s="2"/>
       <c r="Q456" t="s" s="2">
@@ -55428,7 +55481,7 @@
         <v>78</v>
       </c>
       <c r="AG456" t="s" s="2">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="AH456" t="s" s="2">
         <v>76</v>
@@ -55445,13 +55498,13 @@
     </row>
     <row r="457">
       <c r="A457" t="s" s="2">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B457" t="s" s="2">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="C457" t="s" s="2">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="D457" s="2"/>
       <c r="E457" t="s" s="2">
@@ -55477,10 +55530,10 @@
         <v>79</v>
       </c>
       <c r="M457" t="s" s="2">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="N457" t="s" s="2">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="O457" s="2"/>
       <c r="P457" s="2"/>
@@ -55531,7 +55584,7 @@
         <v>78</v>
       </c>
       <c r="AG457" t="s" s="2">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="AH457" t="s" s="2">
         <v>76</v>
@@ -55548,13 +55601,13 @@
     </row>
     <row r="458">
       <c r="A458" t="s" s="2">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B458" t="s" s="2">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="C458" t="s" s="2">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="D458" s="2"/>
       <c r="E458" t="s" s="2">
@@ -55580,10 +55633,10 @@
         <v>86</v>
       </c>
       <c r="M458" t="s" s="2">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="N458" t="s" s="2">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="O458" s="2"/>
       <c r="P458" s="2"/>
@@ -55634,7 +55687,7 @@
         <v>78</v>
       </c>
       <c r="AG458" t="s" s="2">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="AH458" t="s" s="2">
         <v>84</v>
@@ -55651,13 +55704,13 @@
     </row>
     <row r="459">
       <c r="A459" t="s" s="2">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B459" t="s" s="2">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="C459" t="s" s="2">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="D459" s="2"/>
       <c r="E459" t="s" s="2">
@@ -55680,13 +55733,13 @@
         <v>78</v>
       </c>
       <c r="L459" t="s" s="2">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="M459" t="s" s="2">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="N459" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="O459" s="2"/>
       <c r="P459" s="2"/>
@@ -55737,7 +55790,7 @@
         <v>78</v>
       </c>
       <c r="AG459" t="s" s="2">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="AH459" t="s" s="2">
         <v>84</v>
@@ -55754,13 +55807,13 @@
     </row>
     <row r="460">
       <c r="A460" t="s" s="2">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B460" t="s" s="2">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="C460" t="s" s="2">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="D460" s="2"/>
       <c r="E460" t="s" s="2">
@@ -55783,13 +55836,13 @@
         <v>78</v>
       </c>
       <c r="L460" t="s" s="2">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="M460" t="s" s="2">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="N460" t="s" s="2">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="O460" s="2"/>
       <c r="P460" s="2"/>
@@ -55840,7 +55893,7 @@
         <v>78</v>
       </c>
       <c r="AG460" t="s" s="2">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="AH460" t="s" s="2">
         <v>84</v>
@@ -55857,13 +55910,13 @@
     </row>
     <row r="461">
       <c r="A461" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B461" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="C461" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="D461" s="2"/>
       <c r="E461" t="s" s="2">
@@ -55889,10 +55942,10 @@
         <v>79</v>
       </c>
       <c r="M461" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="N461" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="O461" s="2"/>
       <c r="P461" s="2"/>
@@ -55943,7 +55996,7 @@
         <v>78</v>
       </c>
       <c r="AG461" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="AH461" t="s" s="2">
         <v>76</v>
@@ -55955,18 +56008,18 @@
         <v>78</v>
       </c>
       <c r="AK461" t="s" s="2">
-        <v>1258</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B462" t="s" s="2">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="C462" t="s" s="2">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="D462" s="2"/>
       <c r="E462" t="s" s="2">
@@ -56065,13 +56118,13 @@
     </row>
     <row r="463">
       <c r="A463" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B463" t="s" s="2">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="C463" t="s" s="2">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="D463" s="2"/>
       <c r="E463" t="s" s="2">
@@ -56168,13 +56221,13 @@
     </row>
     <row r="464">
       <c r="A464" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B464" t="s" s="2">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="C464" t="s" s="2">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="D464" s="2"/>
       <c r="E464" t="s" s="2">
@@ -56273,13 +56326,13 @@
     </row>
     <row r="465">
       <c r="A465" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B465" t="s" s="2">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="C465" t="s" s="2">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="D465" s="2"/>
       <c r="E465" t="s" s="2">
@@ -56378,13 +56431,13 @@
     </row>
     <row r="466">
       <c r="A466" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B466" t="s" s="2">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="C466" t="s" s="2">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="D466" s="2"/>
       <c r="E466" t="s" s="2">
@@ -56483,13 +56536,13 @@
     </row>
     <row r="467">
       <c r="A467" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B467" t="s" s="2">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="C467" t="s" s="2">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="D467" s="2"/>
       <c r="E467" t="s" s="2">
@@ -56588,13 +56641,13 @@
     </row>
     <row r="468">
       <c r="A468" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B468" t="s" s="2">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="C468" t="s" s="2">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D468" s="2"/>
       <c r="E468" t="s" s="2">
@@ -56693,13 +56746,13 @@
     </row>
     <row r="469">
       <c r="A469" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B469" t="s" s="2">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="C469" t="s" s="2">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="D469" s="2"/>
       <c r="E469" t="s" s="2">
@@ -56800,13 +56853,13 @@
     </row>
     <row r="470">
       <c r="A470" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B470" t="s" s="2">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="C470" t="s" s="2">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="D470" s="2"/>
       <c r="E470" t="s" s="2">
@@ -56814,7 +56867,7 @@
       </c>
       <c r="F470" s="2"/>
       <c r="G470" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H470" t="s" s="2">
         <v>77</v>
@@ -56832,14 +56885,14 @@
         <v>142</v>
       </c>
       <c r="M470" t="s" s="2">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="N470" t="s" s="2">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="O470" s="2"/>
       <c r="P470" t="s" s="2">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="Q470" t="s" s="2">
         <v>78</v>
@@ -56886,7 +56939,7 @@
         <v>147</v>
       </c>
       <c r="AG470" t="s" s="2">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="AH470" t="s" s="2">
         <v>76</v>
@@ -56895,7 +56948,7 @@
         <v>77</v>
       </c>
       <c r="AJ470" t="s" s="2">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="AK470" t="s" s="2">
         <v>96</v>
@@ -56903,23 +56956,23 @@
     </row>
     <row r="471">
       <c r="A471" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B471" t="s" s="2">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="C471" t="s" s="2">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="D471" t="s" s="2">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="E471" t="s" s="2">
         <v>78</v>
       </c>
       <c r="F471" s="2"/>
       <c r="G471" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H471" t="s" s="2">
         <v>84</v>
@@ -56937,14 +56990,14 @@
         <v>142</v>
       </c>
       <c r="M471" t="s" s="2">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="N471" t="s" s="2">
-        <v>1269</v>
+        <v>1276</v>
       </c>
       <c r="O471" s="2"/>
       <c r="P471" t="s" s="2">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="Q471" t="s" s="2">
         <v>78</v>
@@ -56993,7 +57046,7 @@
         <v>78</v>
       </c>
       <c r="AG471" t="s" s="2">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="AH471" t="s" s="2">
         <v>76</v>
@@ -57002,21 +57055,21 @@
         <v>77</v>
       </c>
       <c r="AJ471" t="s" s="2">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="AK471" t="s" s="2">
-        <v>96</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B472" t="s" s="2">
-        <v>1275</v>
+        <v>1278</v>
       </c>
       <c r="C472" t="s" s="2">
-        <v>1276</v>
+        <v>1279</v>
       </c>
       <c r="D472" s="2"/>
       <c r="E472" t="s" s="2">
@@ -57113,13 +57166,13 @@
     </row>
     <row r="473">
       <c r="A473" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B473" t="s" s="2">
-        <v>1277</v>
+        <v>1280</v>
       </c>
       <c r="C473" t="s" s="2">
-        <v>1278</v>
+        <v>1281</v>
       </c>
       <c r="D473" s="2"/>
       <c r="E473" t="s" s="2">
@@ -57218,13 +57271,13 @@
     </row>
     <row r="474">
       <c r="A474" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B474" t="s" s="2">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="C474" t="s" s="2">
-        <v>1280</v>
+        <v>1283</v>
       </c>
       <c r="D474" s="2"/>
       <c r="E474" t="s" s="2">
@@ -57325,13 +57378,13 @@
     </row>
     <row r="475">
       <c r="A475" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B475" t="s" s="2">
-        <v>1281</v>
+        <v>1284</v>
       </c>
       <c r="C475" t="s" s="2">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="D475" s="2"/>
       <c r="E475" t="s" s="2">
@@ -57432,13 +57485,13 @@
     </row>
     <row r="476">
       <c r="A476" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B476" t="s" s="2">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="C476" t="s" s="2">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="D476" s="2"/>
       <c r="E476" t="s" s="2">
@@ -57483,7 +57536,7 @@
         <v>78</v>
       </c>
       <c r="T476" t="s" s="2">
-        <v>1285</v>
+        <v>1288</v>
       </c>
       <c r="U476" t="s" s="2">
         <v>190</v>
@@ -57539,13 +57592,13 @@
     </row>
     <row r="477">
       <c r="A477" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B477" t="s" s="2">
-        <v>1286</v>
+        <v>1289</v>
       </c>
       <c r="C477" t="s" s="2">
-        <v>1287</v>
+        <v>1290</v>
       </c>
       <c r="D477" s="2"/>
       <c r="E477" t="s" s="2">
@@ -57571,7 +57624,7 @@
         <v>194</v>
       </c>
       <c r="M477" t="s" s="2">
-        <v>1288</v>
+        <v>1291</v>
       </c>
       <c r="N477" t="s" s="2">
         <v>196</v>
@@ -57644,13 +57697,13 @@
     </row>
     <row r="478">
       <c r="A478" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B478" t="s" s="2">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="C478" t="s" s="2">
-        <v>1290</v>
+        <v>1293</v>
       </c>
       <c r="D478" s="2"/>
       <c r="E478" t="s" s="2">
@@ -57747,13 +57800,13 @@
     </row>
     <row r="479">
       <c r="A479" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B479" t="s" s="2">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="C479" t="s" s="2">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="D479" s="2"/>
       <c r="E479" t="s" s="2">
@@ -57852,15 +57905,17 @@
     </row>
     <row r="480">
       <c r="A480" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B480" t="s" s="2">
-        <v>1293</v>
+        <v>1296</v>
       </c>
       <c r="C480" t="s" s="2">
-        <v>1293</v>
-      </c>
-      <c r="D480" s="2"/>
+        <v>1268</v>
+      </c>
+      <c r="D480" t="s" s="2">
+        <v>1297</v>
+      </c>
       <c r="E480" t="s" s="2">
         <v>78</v>
       </c>
@@ -57872,35 +57927,31 @@
         <v>84</v>
       </c>
       <c r="I480" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J480" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="K480" t="s" s="2">
         <v>85</v>
       </c>
       <c r="L480" t="s" s="2">
-        <v>215</v>
+        <v>142</v>
       </c>
       <c r="M480" t="s" s="2">
-        <v>1294</v>
+        <v>1298</v>
       </c>
       <c r="N480" t="s" s="2">
-        <v>1295</v>
-      </c>
-      <c r="O480" t="s" s="2">
-        <v>1296</v>
-      </c>
+        <v>1270</v>
+      </c>
+      <c r="O480" s="2"/>
       <c r="P480" t="s" s="2">
-        <v>1297</v>
+        <v>1271</v>
       </c>
       <c r="Q480" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="R480" t="s" s="2">
-        <v>220</v>
-      </c>
+      <c r="R480" s="2"/>
       <c r="S480" t="s" s="2">
         <v>78</v>
       </c>
@@ -57944,30 +57995,30 @@
         <v>78</v>
       </c>
       <c r="AG480" t="s" s="2">
-        <v>1293</v>
+        <v>1268</v>
       </c>
       <c r="AH480" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI480" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ480" t="s" s="2">
-        <v>78</v>
+        <v>1272</v>
       </c>
       <c r="AK480" t="s" s="2">
-        <v>96</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B481" t="s" s="2">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="C481" t="s" s="2">
-        <v>1298</v>
+        <v>1279</v>
       </c>
       <c r="D481" s="2"/>
       <c r="E481" t="s" s="2">
@@ -57978,7 +58029,7 @@
         <v>76</v>
       </c>
       <c r="H481" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I481" t="s" s="2">
         <v>78</v>
@@ -57987,23 +58038,19 @@
         <v>78</v>
       </c>
       <c r="K481" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L481" t="s" s="2">
-        <v>174</v>
+        <v>86</v>
       </c>
       <c r="M481" t="s" s="2">
-        <v>1299</v>
+        <v>153</v>
       </c>
       <c r="N481" t="s" s="2">
-        <v>1300</v>
-      </c>
-      <c r="O481" t="s" s="2">
-        <v>1301</v>
-      </c>
-      <c r="P481" t="s" s="2">
-        <v>1302</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="O481" s="2"/>
+      <c r="P481" s="2"/>
       <c r="Q481" t="s" s="2">
         <v>78</v>
       </c>
@@ -58027,13 +58074,13 @@
         <v>78</v>
       </c>
       <c r="Y481" t="s" s="2">
-        <v>517</v>
+        <v>78</v>
       </c>
       <c r="Z481" t="s" s="2">
-        <v>1303</v>
+        <v>78</v>
       </c>
       <c r="AA481" t="s" s="2">
-        <v>1304</v>
+        <v>78</v>
       </c>
       <c r="AB481" t="s" s="2">
         <v>78</v>
@@ -58051,66 +58098,64 @@
         <v>78</v>
       </c>
       <c r="AG481" t="s" s="2">
-        <v>1298</v>
+        <v>155</v>
       </c>
       <c r="AH481" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI481" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ481" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AK481" t="s" s="2">
-        <v>96</v>
+        <v>78</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B482" t="s" s="2">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="C482" t="s" s="2">
-        <v>1305</v>
+        <v>1281</v>
       </c>
       <c r="D482" s="2"/>
       <c r="E482" t="s" s="2">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="F482" s="2"/>
       <c r="G482" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H482" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I482" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J482" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K482" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L482" t="s" s="2">
-        <v>194</v>
+        <v>130</v>
       </c>
       <c r="M482" t="s" s="2">
-        <v>1306</v>
+        <v>131</v>
       </c>
       <c r="N482" t="s" s="2">
-        <v>1307</v>
+        <v>159</v>
       </c>
       <c r="O482" t="s" s="2">
-        <v>1308</v>
-      </c>
-      <c r="P482" t="s" s="2">
-        <v>1309</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="P482" s="2"/>
       <c r="Q482" t="s" s="2">
         <v>78</v>
       </c>
@@ -58146,42 +58191,42 @@
         <v>78</v>
       </c>
       <c r="AC482" t="s" s="2">
-        <v>78</v>
+        <v>160</v>
       </c>
       <c r="AD482" t="s" s="2">
-        <v>78</v>
+        <v>161</v>
       </c>
       <c r="AE482" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AF482" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="AG482" t="s" s="2">
-        <v>1305</v>
+        <v>162</v>
       </c>
       <c r="AH482" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI482" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ482" t="s" s="2">
-        <v>1271</v>
+        <v>78</v>
       </c>
       <c r="AK482" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B483" t="s" s="2">
-        <v>1310</v>
+        <v>1302</v>
       </c>
       <c r="C483" t="s" s="2">
-        <v>1310</v>
+        <v>1283</v>
       </c>
       <c r="D483" s="2"/>
       <c r="E483" t="s" s="2">
@@ -58192,31 +58237,31 @@
         <v>76</v>
       </c>
       <c r="H483" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I483" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J483" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="K483" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L483" t="s" s="2">
-        <v>194</v>
+        <v>104</v>
       </c>
       <c r="M483" t="s" s="2">
-        <v>1311</v>
+        <v>165</v>
       </c>
       <c r="N483" t="s" s="2">
-        <v>1312</v>
+        <v>166</v>
       </c>
       <c r="O483" t="s" s="2">
-        <v>1313</v>
+        <v>167</v>
       </c>
       <c r="P483" t="s" s="2">
-        <v>1314</v>
+        <v>168</v>
       </c>
       <c r="Q483" t="s" s="2">
         <v>78</v>
@@ -58241,13 +58286,13 @@
         <v>78</v>
       </c>
       <c r="Y483" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="Z483" t="s" s="2">
-        <v>78</v>
+        <v>169</v>
       </c>
       <c r="AA483" t="s" s="2">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="AB483" t="s" s="2">
         <v>78</v>
@@ -58265,13 +58310,13 @@
         <v>78</v>
       </c>
       <c r="AG483" t="s" s="2">
-        <v>1310</v>
+        <v>171</v>
       </c>
       <c r="AH483" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI483" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ483" t="s" s="2">
         <v>78</v>
@@ -58282,13 +58327,13 @@
     </row>
     <row r="484">
       <c r="A484" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B484" t="s" s="2">
-        <v>1315</v>
+        <v>1303</v>
       </c>
       <c r="C484" t="s" s="2">
-        <v>1315</v>
+        <v>1285</v>
       </c>
       <c r="D484" s="2"/>
       <c r="E484" t="s" s="2">
@@ -58311,17 +58356,19 @@
         <v>85</v>
       </c>
       <c r="L484" t="s" s="2">
-        <v>673</v>
+        <v>174</v>
       </c>
       <c r="M484" t="s" s="2">
-        <v>1316</v>
+        <v>175</v>
       </c>
       <c r="N484" t="s" s="2">
-        <v>1317</v>
-      </c>
-      <c r="O484" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="O484" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="P484" t="s" s="2">
-        <v>1318</v>
+        <v>178</v>
       </c>
       <c r="Q484" t="s" s="2">
         <v>78</v>
@@ -58346,13 +58393,13 @@
         <v>78</v>
       </c>
       <c r="Y484" t="s" s="2">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="Z484" t="s" s="2">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="AA484" t="s" s="2">
-        <v>78</v>
+        <v>181</v>
       </c>
       <c r="AB484" t="s" s="2">
         <v>78</v>
@@ -58370,7 +58417,7 @@
         <v>78</v>
       </c>
       <c r="AG484" t="s" s="2">
-        <v>1315</v>
+        <v>182</v>
       </c>
       <c r="AH484" t="s" s="2">
         <v>76</v>
@@ -58387,13 +58434,13 @@
     </row>
     <row r="485">
       <c r="A485" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B485" t="s" s="2">
-        <v>1319</v>
+        <v>1304</v>
       </c>
       <c r="C485" t="s" s="2">
-        <v>1319</v>
+        <v>1287</v>
       </c>
       <c r="D485" s="2"/>
       <c r="E485" t="s" s="2">
@@ -58401,10 +58448,10 @@
       </c>
       <c r="F485" s="2"/>
       <c r="G485" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H485" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I485" t="s" s="2">
         <v>78</v>
@@ -58413,22 +58460,22 @@
         <v>78</v>
       </c>
       <c r="K485" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L485" t="s" s="2">
-        <v>535</v>
+        <v>98</v>
       </c>
       <c r="M485" t="s" s="2">
-        <v>1320</v>
+        <v>185</v>
       </c>
       <c r="N485" t="s" s="2">
-        <v>1321</v>
+        <v>186</v>
       </c>
       <c r="O485" t="s" s="2">
-        <v>1322</v>
+        <v>187</v>
       </c>
       <c r="P485" t="s" s="2">
-        <v>1323</v>
+        <v>188</v>
       </c>
       <c r="Q485" t="s" s="2">
         <v>78</v>
@@ -58438,10 +58485,10 @@
         <v>78</v>
       </c>
       <c r="T485" t="s" s="2">
-        <v>78</v>
+        <v>1305</v>
       </c>
       <c r="U485" t="s" s="2">
-        <v>78</v>
+        <v>190</v>
       </c>
       <c r="V485" t="s" s="2">
         <v>78</v>
@@ -58477,30 +58524,30 @@
         <v>78</v>
       </c>
       <c r="AG485" t="s" s="2">
-        <v>1319</v>
+        <v>191</v>
       </c>
       <c r="AH485" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI485" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ485" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK485" t="s" s="2">
-        <v>1324</v>
+        <v>96</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B486" t="s" s="2">
-        <v>1325</v>
+        <v>1306</v>
       </c>
       <c r="C486" t="s" s="2">
-        <v>1325</v>
+        <v>1290</v>
       </c>
       <c r="D486" s="2"/>
       <c r="E486" t="s" s="2">
@@ -58508,13 +58555,13 @@
       </c>
       <c r="F486" s="2"/>
       <c r="G486" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H486" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I486" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J486" t="s" s="2">
         <v>78</v>
@@ -58523,18 +58570,18 @@
         <v>85</v>
       </c>
       <c r="L486" t="s" s="2">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="M486" t="s" s="2">
-        <v>1326</v>
+        <v>1307</v>
       </c>
       <c r="N486" t="s" s="2">
-        <v>1327</v>
-      </c>
-      <c r="O486" s="2"/>
-      <c r="P486" t="s" s="2">
-        <v>1328</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="O486" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="P486" s="2"/>
       <c r="Q486" t="s" s="2">
         <v>78</v>
       </c>
@@ -58546,7 +58593,7 @@
         <v>78</v>
       </c>
       <c r="U486" t="s" s="2">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="V486" t="s" s="2">
         <v>78</v>
@@ -58582,7 +58629,7 @@
         <v>78</v>
       </c>
       <c r="AG486" t="s" s="2">
-        <v>1325</v>
+        <v>199</v>
       </c>
       <c r="AH486" t="s" s="2">
         <v>76</v>
@@ -58591,7 +58638,7 @@
         <v>84</v>
       </c>
       <c r="AJ486" t="s" s="2">
-        <v>78</v>
+        <v>200</v>
       </c>
       <c r="AK486" t="s" s="2">
         <v>96</v>
@@ -58599,13 +58646,13 @@
     </row>
     <row r="487">
       <c r="A487" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B487" t="s" s="2">
-        <v>1329</v>
+        <v>1308</v>
       </c>
       <c r="C487" t="s" s="2">
-        <v>1329</v>
+        <v>1293</v>
       </c>
       <c r="D487" s="2"/>
       <c r="E487" t="s" s="2">
@@ -58616,30 +58663,28 @@
         <v>76</v>
       </c>
       <c r="H487" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I487" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J487" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K487" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="J487" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K487" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="L487" t="s" s="2">
-        <v>579</v>
+        <v>203</v>
       </c>
       <c r="M487" t="s" s="2">
-        <v>1330</v>
+        <v>204</v>
       </c>
       <c r="N487" t="s" s="2">
-        <v>1331</v>
+        <v>205</v>
       </c>
       <c r="O487" s="2"/>
-      <c r="P487" t="s" s="2">
-        <v>1332</v>
-      </c>
+      <c r="P487" s="2"/>
       <c r="Q487" t="s" s="2">
         <v>78</v>
       </c>
@@ -58687,13 +58732,13 @@
         <v>78</v>
       </c>
       <c r="AG487" t="s" s="2">
-        <v>1329</v>
+        <v>206</v>
       </c>
       <c r="AH487" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI487" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ487" t="s" s="2">
         <v>78</v>
@@ -58704,13 +58749,13 @@
     </row>
     <row r="488">
       <c r="A488" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B488" t="s" s="2">
-        <v>1333</v>
+        <v>1309</v>
       </c>
       <c r="C488" t="s" s="2">
-        <v>1333</v>
+        <v>1295</v>
       </c>
       <c r="D488" s="2"/>
       <c r="E488" t="s" s="2">
@@ -58721,7 +58766,7 @@
         <v>76</v>
       </c>
       <c r="H488" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I488" t="s" s="2">
         <v>78</v>
@@ -58730,18 +58775,20 @@
         <v>78</v>
       </c>
       <c r="K488" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L488" t="s" s="2">
-        <v>383</v>
+        <v>209</v>
       </c>
       <c r="M488" t="s" s="2">
-        <v>1334</v>
+        <v>210</v>
       </c>
       <c r="N488" t="s" s="2">
-        <v>1335</v>
-      </c>
-      <c r="O488" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="O488" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P488" s="2"/>
       <c r="Q488" t="s" s="2">
         <v>78</v>
@@ -58790,13 +58837,13 @@
         <v>78</v>
       </c>
       <c r="AG488" t="s" s="2">
-        <v>1333</v>
+        <v>213</v>
       </c>
       <c r="AH488" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI488" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ488" t="s" s="2">
         <v>78</v>
@@ -58807,13 +58854,13 @@
     </row>
     <row r="489">
       <c r="A489" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B489" t="s" s="2">
-        <v>1336</v>
+        <v>1310</v>
       </c>
       <c r="C489" t="s" s="2">
-        <v>1336</v>
+        <v>1310</v>
       </c>
       <c r="D489" s="2"/>
       <c r="E489" t="s" s="2">
@@ -58830,26 +58877,32 @@
         <v>78</v>
       </c>
       <c r="J489" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="K489" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L489" t="s" s="2">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="M489" t="s" s="2">
-        <v>153</v>
+        <v>1311</v>
       </c>
       <c r="N489" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O489" s="2"/>
-      <c r="P489" s="2"/>
+        <v>1312</v>
+      </c>
+      <c r="O489" t="s" s="2">
+        <v>1313</v>
+      </c>
+      <c r="P489" t="s" s="2">
+        <v>1314</v>
+      </c>
       <c r="Q489" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="R489" s="2"/>
+      <c r="R489" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="S489" t="s" s="2">
         <v>78</v>
       </c>
@@ -58893,7 +58946,7 @@
         <v>78</v>
       </c>
       <c r="AG489" t="s" s="2">
-        <v>155</v>
+        <v>1310</v>
       </c>
       <c r="AH489" t="s" s="2">
         <v>76</v>
@@ -58902,25 +58955,25 @@
         <v>84</v>
       </c>
       <c r="AJ489" t="s" s="2">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="AK489" t="s" s="2">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B490" t="s" s="2">
-        <v>1337</v>
+        <v>1315</v>
       </c>
       <c r="C490" t="s" s="2">
-        <v>1337</v>
+        <v>1315</v>
       </c>
       <c r="D490" s="2"/>
       <c r="E490" t="s" s="2">
-        <v>129</v>
+        <v>78</v>
       </c>
       <c r="F490" s="2"/>
       <c r="G490" t="s" s="2">
@@ -58936,21 +58989,23 @@
         <v>78</v>
       </c>
       <c r="K490" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L490" t="s" s="2">
-        <v>130</v>
+        <v>174</v>
       </c>
       <c r="M490" t="s" s="2">
-        <v>131</v>
+        <v>1316</v>
       </c>
       <c r="N490" t="s" s="2">
-        <v>159</v>
+        <v>1317</v>
       </c>
       <c r="O490" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="P490" s="2"/>
+        <v>1318</v>
+      </c>
+      <c r="P490" t="s" s="2">
+        <v>1319</v>
+      </c>
       <c r="Q490" t="s" s="2">
         <v>78</v>
       </c>
@@ -58974,13 +59029,13 @@
         <v>78</v>
       </c>
       <c r="Y490" t="s" s="2">
-        <v>78</v>
+        <v>517</v>
       </c>
       <c r="Z490" t="s" s="2">
-        <v>78</v>
+        <v>1320</v>
       </c>
       <c r="AA490" t="s" s="2">
-        <v>78</v>
+        <v>1321</v>
       </c>
       <c r="AB490" t="s" s="2">
         <v>78</v>
@@ -58998,7 +59053,7 @@
         <v>78</v>
       </c>
       <c r="AG490" t="s" s="2">
-        <v>162</v>
+        <v>1315</v>
       </c>
       <c r="AH490" t="s" s="2">
         <v>76</v>
@@ -59010,53 +59065,53 @@
         <v>78</v>
       </c>
       <c r="AK490" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B491" t="s" s="2">
-        <v>1338</v>
+        <v>1322</v>
       </c>
       <c r="C491" t="s" s="2">
-        <v>1338</v>
+        <v>1322</v>
       </c>
       <c r="D491" s="2"/>
       <c r="E491" t="s" s="2">
-        <v>392</v>
+        <v>78</v>
       </c>
       <c r="F491" s="2"/>
       <c r="G491" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H491" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I491" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J491" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="K491" t="s" s="2">
         <v>85</v>
       </c>
       <c r="L491" t="s" s="2">
-        <v>130</v>
+        <v>194</v>
       </c>
       <c r="M491" t="s" s="2">
-        <v>393</v>
+        <v>1323</v>
       </c>
       <c r="N491" t="s" s="2">
-        <v>394</v>
+        <v>1324</v>
       </c>
       <c r="O491" t="s" s="2">
-        <v>133</v>
+        <v>1325</v>
       </c>
       <c r="P491" t="s" s="2">
-        <v>139</v>
+        <v>1326</v>
       </c>
       <c r="Q491" t="s" s="2">
         <v>78</v>
@@ -59105,30 +59160,30 @@
         <v>78</v>
       </c>
       <c r="AG491" t="s" s="2">
-        <v>395</v>
+        <v>1322</v>
       </c>
       <c r="AH491" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI491" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ491" t="s" s="2">
-        <v>78</v>
+        <v>1272</v>
       </c>
       <c r="AK491" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B492" t="s" s="2">
-        <v>1339</v>
+        <v>1327</v>
       </c>
       <c r="C492" t="s" s="2">
-        <v>1339</v>
+        <v>1327</v>
       </c>
       <c r="D492" s="2"/>
       <c r="E492" t="s" s="2">
@@ -59151,17 +59206,19 @@
         <v>78</v>
       </c>
       <c r="L492" t="s" s="2">
-        <v>142</v>
+        <v>194</v>
       </c>
       <c r="M492" t="s" s="2">
-        <v>1340</v>
+        <v>1328</v>
       </c>
       <c r="N492" t="s" s="2">
-        <v>1341</v>
-      </c>
-      <c r="O492" s="2"/>
+        <v>1329</v>
+      </c>
+      <c r="O492" t="s" s="2">
+        <v>1330</v>
+      </c>
       <c r="P492" t="s" s="2">
-        <v>1342</v>
+        <v>1331</v>
       </c>
       <c r="Q492" t="s" s="2">
         <v>78</v>
@@ -59210,7 +59267,7 @@
         <v>78</v>
       </c>
       <c r="AG492" t="s" s="2">
-        <v>1339</v>
+        <v>1327</v>
       </c>
       <c r="AH492" t="s" s="2">
         <v>76</v>
@@ -59227,13 +59284,13 @@
     </row>
     <row r="493">
       <c r="A493" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B493" t="s" s="2">
-        <v>1343</v>
+        <v>1332</v>
       </c>
       <c r="C493" t="s" s="2">
-        <v>1343</v>
+        <v>1332</v>
       </c>
       <c r="D493" s="2"/>
       <c r="E493" t="s" s="2">
@@ -59241,7 +59298,7 @@
       </c>
       <c r="F493" s="2"/>
       <c r="G493" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H493" t="s" s="2">
         <v>84</v>
@@ -59253,19 +59310,21 @@
         <v>78</v>
       </c>
       <c r="K493" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L493" t="s" s="2">
-        <v>174</v>
+        <v>673</v>
       </c>
       <c r="M493" t="s" s="2">
-        <v>1344</v>
+        <v>1333</v>
       </c>
       <c r="N493" t="s" s="2">
-        <v>1345</v>
+        <v>1334</v>
       </c>
       <c r="O493" s="2"/>
-      <c r="P493" s="2"/>
+      <c r="P493" t="s" s="2">
+        <v>1335</v>
+      </c>
       <c r="Q493" t="s" s="2">
         <v>78</v>
       </c>
@@ -59289,10 +59348,10 @@
         <v>78</v>
       </c>
       <c r="Y493" t="s" s="2">
-        <v>517</v>
+        <v>78</v>
       </c>
       <c r="Z493" t="s" s="2">
-        <v>1346</v>
+        <v>78</v>
       </c>
       <c r="AA493" t="s" s="2">
         <v>78</v>
@@ -59313,10 +59372,10 @@
         <v>78</v>
       </c>
       <c r="AG493" t="s" s="2">
-        <v>1343</v>
+        <v>1332</v>
       </c>
       <c r="AH493" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI493" t="s" s="2">
         <v>84</v>
@@ -59330,13 +59389,13 @@
     </row>
     <row r="494">
       <c r="A494" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B494" t="s" s="2">
-        <v>1347</v>
+        <v>1336</v>
       </c>
       <c r="C494" t="s" s="2">
-        <v>1347</v>
+        <v>1336</v>
       </c>
       <c r="D494" s="2"/>
       <c r="E494" t="s" s="2">
@@ -59347,7 +59406,7 @@
         <v>76</v>
       </c>
       <c r="H494" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I494" t="s" s="2">
         <v>78</v>
@@ -59359,17 +59418,19 @@
         <v>78</v>
       </c>
       <c r="L494" t="s" s="2">
-        <v>203</v>
+        <v>535</v>
       </c>
       <c r="M494" t="s" s="2">
-        <v>1348</v>
+        <v>1337</v>
       </c>
       <c r="N494" t="s" s="2">
-        <v>1349</v>
-      </c>
-      <c r="O494" s="2"/>
+        <v>1338</v>
+      </c>
+      <c r="O494" t="s" s="2">
+        <v>1339</v>
+      </c>
       <c r="P494" t="s" s="2">
-        <v>1350</v>
+        <v>1340</v>
       </c>
       <c r="Q494" t="s" s="2">
         <v>78</v>
@@ -59418,30 +59479,30 @@
         <v>78</v>
       </c>
       <c r="AG494" t="s" s="2">
-        <v>1347</v>
+        <v>1336</v>
       </c>
       <c r="AH494" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI494" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ494" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK494" t="s" s="2">
-        <v>96</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B495" t="s" s="2">
-        <v>1351</v>
+        <v>1342</v>
       </c>
       <c r="C495" t="s" s="2">
-        <v>1351</v>
+        <v>1342</v>
       </c>
       <c r="D495" s="2"/>
       <c r="E495" t="s" s="2">
@@ -59455,25 +59516,27 @@
         <v>84</v>
       </c>
       <c r="I495" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J495" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K495" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L495" t="s" s="2">
-        <v>209</v>
+        <v>509</v>
       </c>
       <c r="M495" t="s" s="2">
-        <v>1352</v>
+        <v>1343</v>
       </c>
       <c r="N495" t="s" s="2">
-        <v>1353</v>
+        <v>1344</v>
       </c>
       <c r="O495" s="2"/>
-      <c r="P495" s="2"/>
+      <c r="P495" t="s" s="2">
+        <v>1345</v>
+      </c>
       <c r="Q495" t="s" s="2">
         <v>78</v>
       </c>
@@ -59521,7 +59584,7 @@
         <v>78</v>
       </c>
       <c r="AG495" t="s" s="2">
-        <v>1351</v>
+        <v>1342</v>
       </c>
       <c r="AH495" t="s" s="2">
         <v>76</v>
@@ -59538,17 +59601,17 @@
     </row>
     <row r="496">
       <c r="A496" t="s" s="2">
-        <v>1354</v>
+        <v>1250</v>
       </c>
       <c r="B496" t="s" s="2">
-        <v>1359</v>
+        <v>1346</v>
       </c>
       <c r="C496" t="s" s="2">
-        <v>1359</v>
+        <v>1346</v>
       </c>
       <c r="D496" s="2"/>
       <c r="E496" t="s" s="2">
-        <v>1361</v>
+        <v>78</v>
       </c>
       <c r="F496" s="2"/>
       <c r="G496" t="s" s="2">
@@ -59558,7 +59621,7 @@
         <v>77</v>
       </c>
       <c r="I496" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J496" t="s" s="2">
         <v>78</v>
@@ -59567,18 +59630,18 @@
         <v>78</v>
       </c>
       <c r="L496" t="s" s="2">
-        <v>79</v>
+        <v>579</v>
       </c>
       <c r="M496" t="s" s="2">
-        <v>1362</v>
+        <v>1347</v>
       </c>
       <c r="N496" t="s" s="2">
-        <v>1363</v>
-      </c>
-      <c r="O496" t="s" s="2">
-        <v>1364</v>
-      </c>
-      <c r="P496" s="2"/>
+        <v>1348</v>
+      </c>
+      <c r="O496" s="2"/>
+      <c r="P496" t="s" s="2">
+        <v>1349</v>
+      </c>
       <c r="Q496" t="s" s="2">
         <v>78</v>
       </c>
@@ -59626,7 +59689,7 @@
         <v>78</v>
       </c>
       <c r="AG496" t="s" s="2">
-        <v>1359</v>
+        <v>1346</v>
       </c>
       <c r="AH496" t="s" s="2">
         <v>76</v>
@@ -59638,18 +59701,18 @@
         <v>78</v>
       </c>
       <c r="AK496" t="s" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="s" s="2">
-        <v>1354</v>
+        <v>1250</v>
       </c>
       <c r="B497" t="s" s="2">
-        <v>1365</v>
+        <v>1350</v>
       </c>
       <c r="C497" t="s" s="2">
-        <v>1365</v>
+        <v>1350</v>
       </c>
       <c r="D497" s="2"/>
       <c r="E497" t="s" s="2">
@@ -59660,7 +59723,7 @@
         <v>76</v>
       </c>
       <c r="H497" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I497" t="s" s="2">
         <v>78</v>
@@ -59669,20 +59732,18 @@
         <v>78</v>
       </c>
       <c r="K497" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L497" t="s" s="2">
-        <v>86</v>
+        <v>383</v>
       </c>
       <c r="M497" t="s" s="2">
-        <v>87</v>
+        <v>1351</v>
       </c>
       <c r="N497" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="O497" t="s" s="2">
-        <v>89</v>
-      </c>
+        <v>1352</v>
+      </c>
+      <c r="O497" s="2"/>
       <c r="P497" s="2"/>
       <c r="Q497" t="s" s="2">
         <v>78</v>
@@ -59731,30 +59792,30 @@
         <v>78</v>
       </c>
       <c r="AG497" t="s" s="2">
-        <v>90</v>
+        <v>1350</v>
       </c>
       <c r="AH497" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI497" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ497" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK497" t="s" s="2">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="s" s="2">
-        <v>1354</v>
+        <v>1250</v>
       </c>
       <c r="B498" t="s" s="2">
-        <v>1366</v>
+        <v>1353</v>
       </c>
       <c r="C498" t="s" s="2">
-        <v>1366</v>
+        <v>1353</v>
       </c>
       <c r="D498" s="2"/>
       <c r="E498" t="s" s="2">
@@ -59774,16 +59835,16 @@
         <v>78</v>
       </c>
       <c r="K498" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L498" t="s" s="2">
-        <v>92</v>
+        <v>194</v>
       </c>
       <c r="M498" t="s" s="2">
-        <v>93</v>
+        <v>153</v>
       </c>
       <c r="N498" t="s" s="2">
-        <v>94</v>
+        <v>154</v>
       </c>
       <c r="O498" s="2"/>
       <c r="P498" s="2"/>
@@ -59834,7 +59895,7 @@
         <v>78</v>
       </c>
       <c r="AG498" t="s" s="2">
-        <v>95</v>
+        <v>155</v>
       </c>
       <c r="AH498" t="s" s="2">
         <v>76</v>
@@ -59843,53 +59904,53 @@
         <v>84</v>
       </c>
       <c r="AJ498" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AK498" t="s" s="2">
-        <v>96</v>
+        <v>78</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="s" s="2">
+        <v>1250</v>
+      </c>
+      <c r="B499" t="s" s="2">
         <v>1354</v>
       </c>
-      <c r="B499" t="s" s="2">
-        <v>1367</v>
-      </c>
       <c r="C499" t="s" s="2">
-        <v>1367</v>
+        <v>1354</v>
       </c>
       <c r="D499" s="2"/>
       <c r="E499" t="s" s="2">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="F499" s="2"/>
       <c r="G499" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H499" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I499" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J499" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="K499" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L499" t="s" s="2">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="M499" t="s" s="2">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="N499" t="s" s="2">
-        <v>100</v>
+        <v>159</v>
       </c>
       <c r="O499" t="s" s="2">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="P499" s="2"/>
       <c r="Q499" t="s" s="2">
@@ -59939,64 +60000,66 @@
         <v>78</v>
       </c>
       <c r="AG499" t="s" s="2">
-        <v>102</v>
+        <v>162</v>
       </c>
       <c r="AH499" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI499" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ499" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK499" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="s" s="2">
-        <v>1354</v>
+        <v>1250</v>
       </c>
       <c r="B500" t="s" s="2">
-        <v>1368</v>
+        <v>1355</v>
       </c>
       <c r="C500" t="s" s="2">
-        <v>1368</v>
+        <v>1355</v>
       </c>
       <c r="D500" s="2"/>
       <c r="E500" t="s" s="2">
-        <v>78</v>
+        <v>392</v>
       </c>
       <c r="F500" s="2"/>
       <c r="G500" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H500" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I500" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J500" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="K500" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L500" t="s" s="2">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="M500" t="s" s="2">
-        <v>105</v>
+        <v>393</v>
       </c>
       <c r="N500" t="s" s="2">
-        <v>106</v>
+        <v>394</v>
       </c>
       <c r="O500" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="P500" s="2"/>
+        <v>133</v>
+      </c>
+      <c r="P500" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="Q500" t="s" s="2">
         <v>78</v>
       </c>
@@ -60020,13 +60083,13 @@
         <v>78</v>
       </c>
       <c r="Y500" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="Z500" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="AA500" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="AB500" t="s" s="2">
         <v>78</v>
@@ -60044,41 +60107,41 @@
         <v>78</v>
       </c>
       <c r="AG500" t="s" s="2">
-        <v>111</v>
+        <v>395</v>
       </c>
       <c r="AH500" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI500" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ500" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK500" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="s" s="2">
-        <v>1354</v>
+        <v>1250</v>
       </c>
       <c r="B501" t="s" s="2">
-        <v>1369</v>
+        <v>1356</v>
       </c>
       <c r="C501" t="s" s="2">
-        <v>1369</v>
+        <v>1356</v>
       </c>
       <c r="D501" s="2"/>
       <c r="E501" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="F501" s="2"/>
       <c r="G501" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H501" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I501" t="s" s="2">
         <v>78</v>
@@ -60090,18 +60153,18 @@
         <v>78</v>
       </c>
       <c r="L501" t="s" s="2">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="M501" t="s" s="2">
-        <v>115</v>
+        <v>1357</v>
       </c>
       <c r="N501" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="O501" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="P501" s="2"/>
+        <v>1358</v>
+      </c>
+      <c r="O501" s="2"/>
+      <c r="P501" t="s" s="2">
+        <v>1359</v>
+      </c>
       <c r="Q501" t="s" s="2">
         <v>78</v>
       </c>
@@ -60149,16 +60212,16 @@
         <v>78</v>
       </c>
       <c r="AG501" t="s" s="2">
-        <v>118</v>
+        <v>1356</v>
       </c>
       <c r="AH501" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI501" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ501" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK501" t="s" s="2">
         <v>96</v>
@@ -60166,24 +60229,24 @@
     </row>
     <row r="502">
       <c r="A502" t="s" s="2">
-        <v>1354</v>
+        <v>1250</v>
       </c>
       <c r="B502" t="s" s="2">
-        <v>1370</v>
+        <v>1360</v>
       </c>
       <c r="C502" t="s" s="2">
-        <v>1370</v>
+        <v>1360</v>
       </c>
       <c r="D502" s="2"/>
       <c r="E502" t="s" s="2">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="F502" s="2"/>
       <c r="G502" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H502" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I502" t="s" s="2">
         <v>78</v>
@@ -60195,17 +60258,15 @@
         <v>78</v>
       </c>
       <c r="L502" t="s" s="2">
-        <v>122</v>
+        <v>174</v>
       </c>
       <c r="M502" t="s" s="2">
-        <v>123</v>
+        <v>1361</v>
       </c>
       <c r="N502" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="O502" t="s" s="2">
-        <v>125</v>
-      </c>
+        <v>1362</v>
+      </c>
+      <c r="O502" s="2"/>
       <c r="P502" s="2"/>
       <c r="Q502" t="s" s="2">
         <v>78</v>
@@ -60230,10 +60291,10 @@
         <v>78</v>
       </c>
       <c r="Y502" t="s" s="2">
-        <v>78</v>
+        <v>517</v>
       </c>
       <c r="Z502" t="s" s="2">
-        <v>78</v>
+        <v>1363</v>
       </c>
       <c r="AA502" t="s" s="2">
         <v>78</v>
@@ -60254,41 +60315,41 @@
         <v>78</v>
       </c>
       <c r="AG502" t="s" s="2">
-        <v>126</v>
+        <v>1360</v>
       </c>
       <c r="AH502" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI502" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ502" t="s" s="2">
-        <v>127</v>
+        <v>78</v>
       </c>
       <c r="AK502" t="s" s="2">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="s" s="2">
-        <v>1354</v>
+        <v>1250</v>
       </c>
       <c r="B503" t="s" s="2">
-        <v>1371</v>
+        <v>1364</v>
       </c>
       <c r="C503" t="s" s="2">
-        <v>1371</v>
+        <v>1364</v>
       </c>
       <c r="D503" s="2"/>
       <c r="E503" t="s" s="2">
-        <v>129</v>
+        <v>78</v>
       </c>
       <c r="F503" s="2"/>
       <c r="G503" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H503" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I503" t="s" s="2">
         <v>78</v>
@@ -60300,18 +60361,18 @@
         <v>78</v>
       </c>
       <c r="L503" t="s" s="2">
-        <v>130</v>
+        <v>203</v>
       </c>
       <c r="M503" t="s" s="2">
-        <v>131</v>
+        <v>1365</v>
       </c>
       <c r="N503" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="O503" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="P503" s="2"/>
+        <v>1366</v>
+      </c>
+      <c r="O503" s="2"/>
+      <c r="P503" t="s" s="2">
+        <v>1367</v>
+      </c>
       <c r="Q503" t="s" s="2">
         <v>78</v>
       </c>
@@ -60359,66 +60420,62 @@
         <v>78</v>
       </c>
       <c r="AG503" t="s" s="2">
-        <v>134</v>
+        <v>1364</v>
       </c>
       <c r="AH503" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI503" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ503" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK503" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="s" s="2">
-        <v>1354</v>
+        <v>1250</v>
       </c>
       <c r="B504" t="s" s="2">
-        <v>1372</v>
+        <v>1368</v>
       </c>
       <c r="C504" t="s" s="2">
-        <v>1372</v>
+        <v>1368</v>
       </c>
       <c r="D504" s="2"/>
       <c r="E504" t="s" s="2">
-        <v>129</v>
+        <v>78</v>
       </c>
       <c r="F504" s="2"/>
       <c r="G504" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H504" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I504" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J504" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="K504" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L504" t="s" s="2">
-        <v>130</v>
+        <v>209</v>
       </c>
       <c r="M504" t="s" s="2">
-        <v>137</v>
+        <v>1369</v>
       </c>
       <c r="N504" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O504" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="P504" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>1370</v>
+      </c>
+      <c r="O504" s="2"/>
+      <c r="P504" s="2"/>
       <c r="Q504" t="s" s="2">
         <v>78</v>
       </c>
@@ -60466,62 +60523,62 @@
         <v>78</v>
       </c>
       <c r="AG504" t="s" s="2">
-        <v>140</v>
+        <v>1368</v>
       </c>
       <c r="AH504" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI504" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ504" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK504" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="s" s="2">
-        <v>1354</v>
+        <v>1371</v>
       </c>
       <c r="B505" t="s" s="2">
-        <v>1373</v>
+        <v>1376</v>
       </c>
       <c r="C505" t="s" s="2">
-        <v>1373</v>
+        <v>1376</v>
       </c>
       <c r="D505" s="2"/>
       <c r="E505" t="s" s="2">
-        <v>78</v>
+        <v>1378</v>
       </c>
       <c r="F505" s="2"/>
       <c r="G505" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H505" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I505" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J505" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K505" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L505" t="s" s="2">
-        <v>1374</v>
+        <v>79</v>
       </c>
       <c r="M505" t="s" s="2">
-        <v>1375</v>
+        <v>1379</v>
       </c>
       <c r="N505" t="s" s="2">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="O505" t="s" s="2">
-        <v>1377</v>
+        <v>1381</v>
       </c>
       <c r="P505" s="2"/>
       <c r="Q505" t="s" s="2">
@@ -60571,10 +60628,10 @@
         <v>78</v>
       </c>
       <c r="AG505" t="s" s="2">
-        <v>1373</v>
+        <v>1376</v>
       </c>
       <c r="AH505" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI505" t="s" s="2">
         <v>77</v>
@@ -60583,18 +60640,18 @@
         <v>78</v>
       </c>
       <c r="AK505" t="s" s="2">
-        <v>96</v>
+        <v>82</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="s" s="2">
-        <v>1354</v>
+        <v>1371</v>
       </c>
       <c r="B506" t="s" s="2">
-        <v>1378</v>
+        <v>1382</v>
       </c>
       <c r="C506" t="s" s="2">
-        <v>1378</v>
+        <v>1382</v>
       </c>
       <c r="D506" s="2"/>
       <c r="E506" t="s" s="2">
@@ -60614,19 +60671,19 @@
         <v>78</v>
       </c>
       <c r="K506" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L506" t="s" s="2">
-        <v>1379</v>
+        <v>86</v>
       </c>
       <c r="M506" t="s" s="2">
-        <v>1380</v>
+        <v>87</v>
       </c>
       <c r="N506" t="s" s="2">
-        <v>1381</v>
+        <v>88</v>
       </c>
       <c r="O506" t="s" s="2">
-        <v>1382</v>
+        <v>89</v>
       </c>
       <c r="P506" s="2"/>
       <c r="Q506" t="s" s="2">
@@ -60676,7 +60733,7 @@
         <v>78</v>
       </c>
       <c r="AG506" t="s" s="2">
-        <v>1378</v>
+        <v>90</v>
       </c>
       <c r="AH506" t="s" s="2">
         <v>76</v>
@@ -60688,12 +60745,12 @@
         <v>78</v>
       </c>
       <c r="AK506" t="s" s="2">
-        <v>96</v>
+        <v>78</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="s" s="2">
-        <v>1354</v>
+        <v>1371</v>
       </c>
       <c r="B507" t="s" s="2">
         <v>1383</v>
@@ -60707,13 +60764,13 @@
       </c>
       <c r="F507" s="2"/>
       <c r="G507" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H507" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I507" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J507" t="s" s="2">
         <v>78</v>
@@ -60722,17 +60779,15 @@
         <v>85</v>
       </c>
       <c r="L507" t="s" s="2">
-        <v>1242</v>
+        <v>92</v>
       </c>
       <c r="M507" t="s" s="2">
-        <v>1384</v>
+        <v>93</v>
       </c>
       <c r="N507" t="s" s="2">
-        <v>1385</v>
-      </c>
-      <c r="O507" t="s" s="2">
-        <v>1386</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="O507" s="2"/>
       <c r="P507" s="2"/>
       <c r="Q507" t="s" s="2">
         <v>78</v>
@@ -60781,7 +60836,7 @@
         <v>78</v>
       </c>
       <c r="AG507" t="s" s="2">
-        <v>1383</v>
+        <v>95</v>
       </c>
       <c r="AH507" t="s" s="2">
         <v>76</v>
@@ -60798,13 +60853,13 @@
     </row>
     <row r="508">
       <c r="A508" t="s" s="2">
-        <v>1354</v>
+        <v>1371</v>
       </c>
       <c r="B508" t="s" s="2">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="C508" t="s" s="2">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="D508" s="2"/>
       <c r="E508" t="s" s="2">
@@ -60815,28 +60870,28 @@
         <v>76</v>
       </c>
       <c r="H508" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I508" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J508" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="K508" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L508" t="s" s="2">
         <v>98</v>
       </c>
       <c r="M508" t="s" s="2">
-        <v>1388</v>
+        <v>99</v>
       </c>
       <c r="N508" t="s" s="2">
-        <v>1389</v>
+        <v>100</v>
       </c>
       <c r="O508" t="s" s="2">
-        <v>1390</v>
+        <v>101</v>
       </c>
       <c r="P508" s="2"/>
       <c r="Q508" t="s" s="2">
@@ -60886,13 +60941,13 @@
         <v>78</v>
       </c>
       <c r="AG508" t="s" s="2">
-        <v>1387</v>
+        <v>102</v>
       </c>
       <c r="AH508" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI508" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ508" t="s" s="2">
         <v>78</v>
@@ -60903,13 +60958,13 @@
     </row>
     <row r="509">
       <c r="A509" t="s" s="2">
-        <v>1354</v>
+        <v>1371</v>
       </c>
       <c r="B509" t="s" s="2">
-        <v>1391</v>
+        <v>1385</v>
       </c>
       <c r="C509" t="s" s="2">
-        <v>1391</v>
+        <v>1385</v>
       </c>
       <c r="D509" s="2"/>
       <c r="E509" t="s" s="2">
@@ -60932,15 +60987,17 @@
         <v>78</v>
       </c>
       <c r="L509" t="s" s="2">
-        <v>527</v>
+        <v>104</v>
       </c>
       <c r="M509" t="s" s="2">
-        <v>1392</v>
+        <v>105</v>
       </c>
       <c r="N509" t="s" s="2">
-        <v>1393</v>
-      </c>
-      <c r="O509" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="O509" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="P509" s="2"/>
       <c r="Q509" t="s" s="2">
         <v>78</v>
@@ -60965,13 +61022,13 @@
         <v>78</v>
       </c>
       <c r="Y509" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="Z509" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="AA509" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="AB509" t="s" s="2">
         <v>78</v>
@@ -60989,7 +61046,7 @@
         <v>78</v>
       </c>
       <c r="AG509" t="s" s="2">
-        <v>1391</v>
+        <v>111</v>
       </c>
       <c r="AH509" t="s" s="2">
         <v>76</v>
@@ -61006,24 +61063,24 @@
     </row>
     <row r="510">
       <c r="A510" t="s" s="2">
-        <v>1354</v>
+        <v>1371</v>
       </c>
       <c r="B510" t="s" s="2">
-        <v>1394</v>
+        <v>1386</v>
       </c>
       <c r="C510" t="s" s="2">
-        <v>1394</v>
+        <v>1386</v>
       </c>
       <c r="D510" s="2"/>
       <c r="E510" t="s" s="2">
-        <v>1395</v>
+        <v>113</v>
       </c>
       <c r="F510" s="2"/>
       <c r="G510" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H510" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I510" t="s" s="2">
         <v>78</v>
@@ -61035,18 +61092,18 @@
         <v>78</v>
       </c>
       <c r="L510" t="s" s="2">
-        <v>1396</v>
+        <v>114</v>
       </c>
       <c r="M510" t="s" s="2">
-        <v>1397</v>
+        <v>115</v>
       </c>
       <c r="N510" t="s" s="2">
-        <v>1398</v>
-      </c>
-      <c r="O510" s="2"/>
-      <c r="P510" t="s" s="2">
-        <v>1399</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="O510" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="P510" s="2"/>
       <c r="Q510" t="s" s="2">
         <v>78</v>
       </c>
@@ -61070,13 +61127,13 @@
         <v>78</v>
       </c>
       <c r="Y510" t="s" s="2">
-        <v>517</v>
+        <v>78</v>
       </c>
       <c r="Z510" t="s" s="2">
-        <v>1400</v>
+        <v>78</v>
       </c>
       <c r="AA510" t="s" s="2">
-        <v>1401</v>
+        <v>78</v>
       </c>
       <c r="AB510" t="s" s="2">
         <v>78</v>
@@ -61094,16 +61151,16 @@
         <v>78</v>
       </c>
       <c r="AG510" t="s" s="2">
-        <v>1394</v>
+        <v>118</v>
       </c>
       <c r="AH510" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI510" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ510" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK510" t="s" s="2">
         <v>96</v>
@@ -61111,24 +61168,24 @@
     </row>
     <row r="511">
       <c r="A511" t="s" s="2">
-        <v>1354</v>
+        <v>1371</v>
       </c>
       <c r="B511" t="s" s="2">
-        <v>1402</v>
+        <v>1387</v>
       </c>
       <c r="C511" t="s" s="2">
-        <v>1402</v>
+        <v>1387</v>
       </c>
       <c r="D511" s="2"/>
       <c r="E511" t="s" s="2">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="F511" s="2"/>
       <c r="G511" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H511" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I511" t="s" s="2">
         <v>78</v>
@@ -61140,15 +61197,17 @@
         <v>78</v>
       </c>
       <c r="L511" t="s" s="2">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="M511" t="s" s="2">
-        <v>1403</v>
+        <v>123</v>
       </c>
       <c r="N511" t="s" s="2">
-        <v>1404</v>
-      </c>
-      <c r="O511" s="2"/>
+        <v>124</v>
+      </c>
+      <c r="O511" t="s" s="2">
+        <v>125</v>
+      </c>
       <c r="P511" s="2"/>
       <c r="Q511" t="s" s="2">
         <v>78</v>
@@ -61173,13 +61232,13 @@
         <v>78</v>
       </c>
       <c r="Y511" t="s" s="2">
-        <v>517</v>
+        <v>78</v>
       </c>
       <c r="Z511" t="s" s="2">
-        <v>1405</v>
+        <v>78</v>
       </c>
       <c r="AA511" t="s" s="2">
-        <v>1406</v>
+        <v>78</v>
       </c>
       <c r="AB511" t="s" s="2">
         <v>78</v>
@@ -61197,34 +61256,34 @@
         <v>78</v>
       </c>
       <c r="AG511" t="s" s="2">
-        <v>1402</v>
+        <v>126</v>
       </c>
       <c r="AH511" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI511" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ511" t="s" s="2">
-        <v>78</v>
+        <v>127</v>
       </c>
       <c r="AK511" t="s" s="2">
-        <v>96</v>
+        <v>78</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="s" s="2">
-        <v>1354</v>
+        <v>1371</v>
       </c>
       <c r="B512" t="s" s="2">
-        <v>1407</v>
+        <v>1388</v>
       </c>
       <c r="C512" t="s" s="2">
-        <v>1407</v>
+        <v>1388</v>
       </c>
       <c r="D512" s="2"/>
       <c r="E512" t="s" s="2">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="F512" s="2"/>
       <c r="G512" t="s" s="2">
@@ -61243,15 +61302,17 @@
         <v>78</v>
       </c>
       <c r="L512" t="s" s="2">
-        <v>1408</v>
+        <v>130</v>
       </c>
       <c r="M512" t="s" s="2">
-        <v>1409</v>
+        <v>131</v>
       </c>
       <c r="N512" t="s" s="2">
-        <v>1410</v>
-      </c>
-      <c r="O512" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="O512" t="s" s="2">
+        <v>133</v>
+      </c>
       <c r="P512" s="2"/>
       <c r="Q512" t="s" s="2">
         <v>78</v>
@@ -61300,7 +61361,7 @@
         <v>78</v>
       </c>
       <c r="AG512" t="s" s="2">
-        <v>1407</v>
+        <v>134</v>
       </c>
       <c r="AH512" t="s" s="2">
         <v>76</v>
@@ -61312,51 +61373,53 @@
         <v>78</v>
       </c>
       <c r="AK512" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="s" s="2">
-        <v>1354</v>
+        <v>1371</v>
       </c>
       <c r="B513" t="s" s="2">
-        <v>1411</v>
+        <v>1389</v>
       </c>
       <c r="C513" t="s" s="2">
-        <v>1411</v>
+        <v>1389</v>
       </c>
       <c r="D513" s="2"/>
       <c r="E513" t="s" s="2">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="F513" s="2"/>
       <c r="G513" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H513" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I513" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J513" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="K513" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L513" t="s" s="2">
-        <v>1412</v>
+        <v>130</v>
       </c>
       <c r="M513" t="s" s="2">
-        <v>1413</v>
+        <v>137</v>
       </c>
       <c r="N513" t="s" s="2">
-        <v>1414</v>
-      </c>
-      <c r="O513" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="O513" t="s" s="2">
+        <v>133</v>
+      </c>
       <c r="P513" t="s" s="2">
-        <v>1415</v>
+        <v>139</v>
       </c>
       <c r="Q513" t="s" s="2">
         <v>78</v>
@@ -61405,30 +61468,30 @@
         <v>78</v>
       </c>
       <c r="AG513" t="s" s="2">
-        <v>1411</v>
+        <v>140</v>
       </c>
       <c r="AH513" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI513" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ513" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK513" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="s" s="2">
-        <v>1354</v>
+        <v>1371</v>
       </c>
       <c r="B514" t="s" s="2">
-        <v>1416</v>
+        <v>1390</v>
       </c>
       <c r="C514" t="s" s="2">
-        <v>1416</v>
+        <v>1390</v>
       </c>
       <c r="D514" s="2"/>
       <c r="E514" t="s" s="2">
@@ -61436,30 +61499,32 @@
       </c>
       <c r="F514" s="2"/>
       <c r="G514" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H514" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I514" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J514" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K514" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L514" t="s" s="2">
-        <v>1417</v>
+        <v>1391</v>
       </c>
       <c r="M514" t="s" s="2">
-        <v>1418</v>
+        <v>1392</v>
       </c>
       <c r="N514" t="s" s="2">
-        <v>1419</v>
-      </c>
-      <c r="O514" s="2"/>
+        <v>1393</v>
+      </c>
+      <c r="O514" t="s" s="2">
+        <v>1394</v>
+      </c>
       <c r="P514" s="2"/>
       <c r="Q514" t="s" s="2">
         <v>78</v>
@@ -61508,13 +61573,13 @@
         <v>78</v>
       </c>
       <c r="AG514" t="s" s="2">
-        <v>1416</v>
+        <v>1390</v>
       </c>
       <c r="AH514" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI514" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ514" t="s" s="2">
         <v>78</v>
@@ -61525,13 +61590,13 @@
     </row>
     <row r="515">
       <c r="A515" t="s" s="2">
-        <v>1354</v>
+        <v>1371</v>
       </c>
       <c r="B515" t="s" s="2">
-        <v>1420</v>
+        <v>1395</v>
       </c>
       <c r="C515" t="s" s="2">
-        <v>1420</v>
+        <v>1395</v>
       </c>
       <c r="D515" s="2"/>
       <c r="E515" t="s" s="2">
@@ -61539,35 +61604,33 @@
       </c>
       <c r="F515" s="2"/>
       <c r="G515" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H515" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I515" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J515" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K515" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L515" t="s" s="2">
-        <v>383</v>
+        <v>1396</v>
       </c>
       <c r="M515" t="s" s="2">
-        <v>1421</v>
+        <v>1397</v>
       </c>
       <c r="N515" t="s" s="2">
-        <v>1422</v>
+        <v>1398</v>
       </c>
       <c r="O515" t="s" s="2">
-        <v>1423</v>
-      </c>
-      <c r="P515" t="s" s="2">
-        <v>1424</v>
-      </c>
+        <v>1399</v>
+      </c>
+      <c r="P515" s="2"/>
       <c r="Q515" t="s" s="2">
         <v>78</v>
       </c>
@@ -61615,30 +61678,30 @@
         <v>78</v>
       </c>
       <c r="AG515" t="s" s="2">
-        <v>1420</v>
+        <v>1395</v>
       </c>
       <c r="AH515" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI515" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ515" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK515" t="s" s="2">
-        <v>1425</v>
+        <v>96</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="s" s="2">
-        <v>1354</v>
+        <v>1371</v>
       </c>
       <c r="B516" t="s" s="2">
-        <v>1426</v>
+        <v>1400</v>
       </c>
       <c r="C516" t="s" s="2">
-        <v>1426</v>
+        <v>1400</v>
       </c>
       <c r="D516" s="2"/>
       <c r="E516" t="s" s="2">
@@ -61646,30 +61709,32 @@
       </c>
       <c r="F516" s="2"/>
       <c r="G516" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H516" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I516" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J516" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K516" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L516" t="s" s="2">
-        <v>194</v>
+        <v>1243</v>
       </c>
       <c r="M516" t="s" s="2">
-        <v>153</v>
+        <v>1401</v>
       </c>
       <c r="N516" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O516" s="2"/>
+        <v>1402</v>
+      </c>
+      <c r="O516" t="s" s="2">
+        <v>1403</v>
+      </c>
       <c r="P516" s="2"/>
       <c r="Q516" t="s" s="2">
         <v>78</v>
@@ -61718,7 +61783,7 @@
         <v>78</v>
       </c>
       <c r="AG516" t="s" s="2">
-        <v>155</v>
+        <v>1400</v>
       </c>
       <c r="AH516" t="s" s="2">
         <v>76</v>
@@ -61727,25 +61792,25 @@
         <v>84</v>
       </c>
       <c r="AJ516" t="s" s="2">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="AK516" t="s" s="2">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="s" s="2">
-        <v>1354</v>
+        <v>1371</v>
       </c>
       <c r="B517" t="s" s="2">
-        <v>1427</v>
+        <v>1404</v>
       </c>
       <c r="C517" t="s" s="2">
-        <v>1427</v>
+        <v>1404</v>
       </c>
       <c r="D517" s="2"/>
       <c r="E517" t="s" s="2">
-        <v>129</v>
+        <v>78</v>
       </c>
       <c r="F517" s="2"/>
       <c r="G517" t="s" s="2">
@@ -61764,16 +61829,16 @@
         <v>78</v>
       </c>
       <c r="L517" t="s" s="2">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="M517" t="s" s="2">
-        <v>131</v>
+        <v>1405</v>
       </c>
       <c r="N517" t="s" s="2">
-        <v>159</v>
+        <v>1406</v>
       </c>
       <c r="O517" t="s" s="2">
-        <v>133</v>
+        <v>1407</v>
       </c>
       <c r="P517" s="2"/>
       <c r="Q517" t="s" s="2">
@@ -61823,7 +61888,7 @@
         <v>78</v>
       </c>
       <c r="AG517" t="s" s="2">
-        <v>162</v>
+        <v>1404</v>
       </c>
       <c r="AH517" t="s" s="2">
         <v>76</v>
@@ -61835,54 +61900,50 @@
         <v>78</v>
       </c>
       <c r="AK517" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="s" s="2">
-        <v>1354</v>
+        <v>1371</v>
       </c>
       <c r="B518" t="s" s="2">
-        <v>1428</v>
+        <v>1408</v>
       </c>
       <c r="C518" t="s" s="2">
-        <v>1428</v>
+        <v>1408</v>
       </c>
       <c r="D518" s="2"/>
       <c r="E518" t="s" s="2">
-        <v>392</v>
+        <v>78</v>
       </c>
       <c r="F518" s="2"/>
       <c r="G518" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H518" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I518" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J518" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="K518" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L518" t="s" s="2">
-        <v>130</v>
+        <v>527</v>
       </c>
       <c r="M518" t="s" s="2">
-        <v>393</v>
+        <v>1409</v>
       </c>
       <c r="N518" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="O518" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="P518" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>1410</v>
+      </c>
+      <c r="O518" s="2"/>
+      <c r="P518" s="2"/>
       <c r="Q518" t="s" s="2">
         <v>78</v>
       </c>
@@ -61930,41 +61991,41 @@
         <v>78</v>
       </c>
       <c r="AG518" t="s" s="2">
-        <v>395</v>
+        <v>1408</v>
       </c>
       <c r="AH518" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI518" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ518" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK518" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="s" s="2">
-        <v>1354</v>
+        <v>1371</v>
       </c>
       <c r="B519" t="s" s="2">
-        <v>1429</v>
+        <v>1411</v>
       </c>
       <c r="C519" t="s" s="2">
-        <v>1429</v>
+        <v>1411</v>
       </c>
       <c r="D519" s="2"/>
       <c r="E519" t="s" s="2">
-        <v>78</v>
+        <v>1412</v>
       </c>
       <c r="F519" s="2"/>
       <c r="G519" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H519" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I519" t="s" s="2">
         <v>78</v>
@@ -61973,22 +62034,20 @@
         <v>78</v>
       </c>
       <c r="K519" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L519" t="s" s="2">
-        <v>174</v>
+        <v>1413</v>
       </c>
       <c r="M519" t="s" s="2">
-        <v>1430</v>
+        <v>1414</v>
       </c>
       <c r="N519" t="s" s="2">
-        <v>1431</v>
-      </c>
-      <c r="O519" t="s" s="2">
-        <v>1432</v>
-      </c>
+        <v>1415</v>
+      </c>
+      <c r="O519" s="2"/>
       <c r="P519" t="s" s="2">
-        <v>1433</v>
+        <v>1416</v>
       </c>
       <c r="Q519" t="s" s="2">
         <v>78</v>
@@ -62016,10 +62075,10 @@
         <v>517</v>
       </c>
       <c r="Z519" t="s" s="2">
-        <v>1434</v>
+        <v>1417</v>
       </c>
       <c r="AA519" t="s" s="2">
-        <v>1435</v>
+        <v>1418</v>
       </c>
       <c r="AB519" t="s" s="2">
         <v>78</v>
@@ -62037,13 +62096,13 @@
         <v>78</v>
       </c>
       <c r="AG519" t="s" s="2">
-        <v>1429</v>
+        <v>1411</v>
       </c>
       <c r="AH519" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI519" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ519" t="s" s="2">
         <v>78</v>
@@ -62054,13 +62113,13 @@
     </row>
     <row r="520">
       <c r="A520" t="s" s="2">
-        <v>1354</v>
+        <v>1371</v>
       </c>
       <c r="B520" t="s" s="2">
-        <v>1436</v>
+        <v>1419</v>
       </c>
       <c r="C520" t="s" s="2">
-        <v>1436</v>
+        <v>1419</v>
       </c>
       <c r="D520" s="2"/>
       <c r="E520" t="s" s="2">
@@ -62071,7 +62130,7 @@
         <v>76</v>
       </c>
       <c r="H520" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I520" t="s" s="2">
         <v>78</v>
@@ -62086,17 +62145,13 @@
         <v>174</v>
       </c>
       <c r="M520" t="s" s="2">
-        <v>1437</v>
+        <v>1420</v>
       </c>
       <c r="N520" t="s" s="2">
-        <v>1438</v>
-      </c>
-      <c r="O520" t="s" s="2">
-        <v>1439</v>
-      </c>
-      <c r="P520" t="s" s="2">
-        <v>1440</v>
-      </c>
+        <v>1421</v>
+      </c>
+      <c r="O520" s="2"/>
+      <c r="P520" s="2"/>
       <c r="Q520" t="s" s="2">
         <v>78</v>
       </c>
@@ -62123,10 +62178,10 @@
         <v>517</v>
       </c>
       <c r="Z520" t="s" s="2">
-        <v>1441</v>
+        <v>1422</v>
       </c>
       <c r="AA520" t="s" s="2">
-        <v>1442</v>
+        <v>1423</v>
       </c>
       <c r="AB520" t="s" s="2">
         <v>78</v>
@@ -62144,13 +62199,13 @@
         <v>78</v>
       </c>
       <c r="AG520" t="s" s="2">
-        <v>1436</v>
+        <v>1419</v>
       </c>
       <c r="AH520" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI520" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ520" t="s" s="2">
         <v>78</v>
@@ -62161,13 +62216,13 @@
     </row>
     <row r="521">
       <c r="A521" t="s" s="2">
-        <v>1354</v>
+        <v>1371</v>
       </c>
       <c r="B521" t="s" s="2">
-        <v>1443</v>
+        <v>1424</v>
       </c>
       <c r="C521" t="s" s="2">
-        <v>1443</v>
+        <v>1424</v>
       </c>
       <c r="D521" s="2"/>
       <c r="E521" t="s" s="2">
@@ -62175,28 +62230,28 @@
       </c>
       <c r="F521" s="2"/>
       <c r="G521" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H521" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I521" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J521" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K521" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L521" t="s" s="2">
-        <v>1444</v>
+        <v>1425</v>
       </c>
       <c r="M521" t="s" s="2">
-        <v>1445</v>
+        <v>1426</v>
       </c>
       <c r="N521" t="s" s="2">
-        <v>1446</v>
+        <v>1427</v>
       </c>
       <c r="O521" s="2"/>
       <c r="P521" s="2"/>
@@ -62247,16 +62302,16 @@
         <v>78</v>
       </c>
       <c r="AG521" t="s" s="2">
-        <v>1443</v>
+        <v>1424</v>
       </c>
       <c r="AH521" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI521" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ521" t="s" s="2">
-        <v>1447</v>
+        <v>78</v>
       </c>
       <c r="AK521" t="s" s="2">
         <v>96</v>
@@ -62264,13 +62319,13 @@
     </row>
     <row r="522">
       <c r="A522" t="s" s="2">
-        <v>1354</v>
+        <v>1371</v>
       </c>
       <c r="B522" t="s" s="2">
-        <v>1448</v>
+        <v>1428</v>
       </c>
       <c r="C522" t="s" s="2">
-        <v>1448</v>
+        <v>1428</v>
       </c>
       <c r="D522" s="2"/>
       <c r="E522" t="s" s="2">
@@ -62293,16 +62348,18 @@
         <v>78</v>
       </c>
       <c r="L522" t="s" s="2">
-        <v>1449</v>
+        <v>1429</v>
       </c>
       <c r="M522" t="s" s="2">
-        <v>1450</v>
+        <v>1430</v>
       </c>
       <c r="N522" t="s" s="2">
-        <v>1451</v>
+        <v>1431</v>
       </c>
       <c r="O522" s="2"/>
-      <c r="P522" s="2"/>
+      <c r="P522" t="s" s="2">
+        <v>1432</v>
+      </c>
       <c r="Q522" t="s" s="2">
         <v>78</v>
       </c>
@@ -62350,7 +62407,7 @@
         <v>78</v>
       </c>
       <c r="AG522" t="s" s="2">
-        <v>1448</v>
+        <v>1428</v>
       </c>
       <c r="AH522" t="s" s="2">
         <v>76</v>
@@ -62359,7 +62416,7 @@
         <v>84</v>
       </c>
       <c r="AJ522" t="s" s="2">
-        <v>1447</v>
+        <v>78</v>
       </c>
       <c r="AK522" t="s" s="2">
         <v>96</v>
@@ -62367,13 +62424,13 @@
     </row>
     <row r="523">
       <c r="A523" t="s" s="2">
-        <v>1354</v>
+        <v>1371</v>
       </c>
       <c r="B523" t="s" s="2">
-        <v>1452</v>
+        <v>1433</v>
       </c>
       <c r="C523" t="s" s="2">
-        <v>1452</v>
+        <v>1433</v>
       </c>
       <c r="D523" s="2"/>
       <c r="E523" t="s" s="2">
@@ -62384,7 +62441,7 @@
         <v>76</v>
       </c>
       <c r="H523" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I523" t="s" s="2">
         <v>78</v>
@@ -62393,16 +62450,16 @@
         <v>78</v>
       </c>
       <c r="K523" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L523" t="s" s="2">
-        <v>383</v>
+        <v>1434</v>
       </c>
       <c r="M523" t="s" s="2">
-        <v>1453</v>
+        <v>1435</v>
       </c>
       <c r="N523" t="s" s="2">
-        <v>1454</v>
+        <v>1436</v>
       </c>
       <c r="O523" s="2"/>
       <c r="P523" s="2"/>
@@ -62453,13 +62510,13 @@
         <v>78</v>
       </c>
       <c r="AG523" t="s" s="2">
-        <v>1452</v>
+        <v>1433</v>
       </c>
       <c r="AH523" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI523" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ523" t="s" s="2">
         <v>78</v>
@@ -62470,13 +62527,13 @@
     </row>
     <row r="524">
       <c r="A524" t="s" s="2">
-        <v>1354</v>
+        <v>1371</v>
       </c>
       <c r="B524" t="s" s="2">
-        <v>1455</v>
+        <v>1437</v>
       </c>
       <c r="C524" t="s" s="2">
-        <v>1455</v>
+        <v>1437</v>
       </c>
       <c r="D524" s="2"/>
       <c r="E524" t="s" s="2">
@@ -62484,31 +62541,35 @@
       </c>
       <c r="F524" s="2"/>
       <c r="G524" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H524" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I524" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J524" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K524" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L524" t="s" s="2">
-        <v>194</v>
+        <v>383</v>
       </c>
       <c r="M524" t="s" s="2">
-        <v>153</v>
+        <v>1438</v>
       </c>
       <c r="N524" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O524" s="2"/>
-      <c r="P524" s="2"/>
+        <v>1439</v>
+      </c>
+      <c r="O524" t="s" s="2">
+        <v>1440</v>
+      </c>
+      <c r="P524" t="s" s="2">
+        <v>1441</v>
+      </c>
       <c r="Q524" t="s" s="2">
         <v>78</v>
       </c>
@@ -62556,41 +62617,41 @@
         <v>78</v>
       </c>
       <c r="AG524" t="s" s="2">
-        <v>155</v>
+        <v>1437</v>
       </c>
       <c r="AH524" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI524" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ524" t="s" s="2">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="AK524" t="s" s="2">
-        <v>78</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="s" s="2">
-        <v>1354</v>
+        <v>1371</v>
       </c>
       <c r="B525" t="s" s="2">
-        <v>1456</v>
+        <v>1443</v>
       </c>
       <c r="C525" t="s" s="2">
-        <v>1456</v>
+        <v>1443</v>
       </c>
       <c r="D525" s="2"/>
       <c r="E525" t="s" s="2">
-        <v>129</v>
+        <v>78</v>
       </c>
       <c r="F525" s="2"/>
       <c r="G525" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H525" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I525" t="s" s="2">
         <v>78</v>
@@ -62602,17 +62663,15 @@
         <v>78</v>
       </c>
       <c r="L525" t="s" s="2">
-        <v>130</v>
+        <v>194</v>
       </c>
       <c r="M525" t="s" s="2">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="N525" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O525" t="s" s="2">
-        <v>133</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="O525" s="2"/>
       <c r="P525" s="2"/>
       <c r="Q525" t="s" s="2">
         <v>78</v>
@@ -62661,34 +62720,34 @@
         <v>78</v>
       </c>
       <c r="AG525" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="AH525" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI525" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ525" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AK525" t="s" s="2">
-        <v>135</v>
+        <v>78</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="s" s="2">
-        <v>1354</v>
+        <v>1371</v>
       </c>
       <c r="B526" t="s" s="2">
-        <v>1457</v>
+        <v>1444</v>
       </c>
       <c r="C526" t="s" s="2">
-        <v>1457</v>
+        <v>1444</v>
       </c>
       <c r="D526" s="2"/>
       <c r="E526" t="s" s="2">
-        <v>392</v>
+        <v>129</v>
       </c>
       <c r="F526" s="2"/>
       <c r="G526" t="s" s="2">
@@ -62701,26 +62760,24 @@
         <v>78</v>
       </c>
       <c r="J526" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="K526" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L526" t="s" s="2">
         <v>130</v>
       </c>
       <c r="M526" t="s" s="2">
-        <v>393</v>
+        <v>131</v>
       </c>
       <c r="N526" t="s" s="2">
-        <v>394</v>
+        <v>159</v>
       </c>
       <c r="O526" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="P526" t="s" s="2">
-        <v>139</v>
-      </c>
+      <c r="P526" s="2"/>
       <c r="Q526" t="s" s="2">
         <v>78</v>
       </c>
@@ -62768,7 +62825,7 @@
         <v>78</v>
       </c>
       <c r="AG526" t="s" s="2">
-        <v>395</v>
+        <v>162</v>
       </c>
       <c r="AH526" t="s" s="2">
         <v>76</v>
@@ -62785,45 +62842,49 @@
     </row>
     <row r="527">
       <c r="A527" t="s" s="2">
-        <v>1354</v>
+        <v>1371</v>
       </c>
       <c r="B527" t="s" s="2">
-        <v>1458</v>
+        <v>1445</v>
       </c>
       <c r="C527" t="s" s="2">
-        <v>1458</v>
+        <v>1445</v>
       </c>
       <c r="D527" s="2"/>
       <c r="E527" t="s" s="2">
-        <v>78</v>
+        <v>392</v>
       </c>
       <c r="F527" s="2"/>
       <c r="G527" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H527" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I527" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J527" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="K527" t="s" s="2">
         <v>85</v>
       </c>
       <c r="L527" t="s" s="2">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="M527" t="s" s="2">
-        <v>1459</v>
+        <v>393</v>
       </c>
       <c r="N527" t="s" s="2">
-        <v>1460</v>
-      </c>
-      <c r="O527" s="2"/>
-      <c r="P527" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="O527" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="P527" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="Q527" t="s" s="2">
         <v>78</v>
       </c>
@@ -62847,13 +62908,13 @@
         <v>78</v>
       </c>
       <c r="Y527" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="Z527" t="s" s="2">
-        <v>1461</v>
+        <v>78</v>
       </c>
       <c r="AA527" t="s" s="2">
-        <v>1462</v>
+        <v>78</v>
       </c>
       <c r="AB527" t="s" s="2">
         <v>78</v>
@@ -62871,30 +62932,30 @@
         <v>78</v>
       </c>
       <c r="AG527" t="s" s="2">
-        <v>1458</v>
+        <v>395</v>
       </c>
       <c r="AH527" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI527" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ527" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK527" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="s" s="2">
-        <v>1354</v>
+        <v>1371</v>
       </c>
       <c r="B528" t="s" s="2">
-        <v>1463</v>
+        <v>1446</v>
       </c>
       <c r="C528" t="s" s="2">
-        <v>1463</v>
+        <v>1446</v>
       </c>
       <c r="D528" s="2"/>
       <c r="E528" t="s" s="2">
@@ -62902,7 +62963,7 @@
       </c>
       <c r="F528" s="2"/>
       <c r="G528" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H528" t="s" s="2">
         <v>84</v>
@@ -62917,18 +62978,20 @@
         <v>85</v>
       </c>
       <c r="L528" t="s" s="2">
-        <v>1464</v>
+        <v>174</v>
       </c>
       <c r="M528" t="s" s="2">
-        <v>1465</v>
+        <v>1447</v>
       </c>
       <c r="N528" t="s" s="2">
-        <v>1466</v>
+        <v>1448</v>
       </c>
       <c r="O528" t="s" s="2">
-        <v>1467</v>
-      </c>
-      <c r="P528" s="2"/>
+        <v>1449</v>
+      </c>
+      <c r="P528" t="s" s="2">
+        <v>1450</v>
+      </c>
       <c r="Q528" t="s" s="2">
         <v>78</v>
       </c>
@@ -62952,13 +63015,13 @@
         <v>78</v>
       </c>
       <c r="Y528" t="s" s="2">
-        <v>78</v>
+        <v>517</v>
       </c>
       <c r="Z528" t="s" s="2">
-        <v>78</v>
+        <v>1451</v>
       </c>
       <c r="AA528" t="s" s="2">
-        <v>78</v>
+        <v>1452</v>
       </c>
       <c r="AB528" t="s" s="2">
         <v>78</v>
@@ -62976,10 +63039,10 @@
         <v>78</v>
       </c>
       <c r="AG528" t="s" s="2">
-        <v>1463</v>
+        <v>1446</v>
       </c>
       <c r="AH528" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI528" t="s" s="2">
         <v>84</v>
@@ -62993,13 +63056,13 @@
     </row>
     <row r="529">
       <c r="A529" t="s" s="2">
-        <v>1354</v>
+        <v>1371</v>
       </c>
       <c r="B529" t="s" s="2">
-        <v>1468</v>
+        <v>1453</v>
       </c>
       <c r="C529" t="s" s="2">
-        <v>1468</v>
+        <v>1453</v>
       </c>
       <c r="D529" s="2"/>
       <c r="E529" t="s" s="2">
@@ -63022,18 +63085,20 @@
         <v>78</v>
       </c>
       <c r="L529" t="s" s="2">
-        <v>79</v>
+        <v>174</v>
       </c>
       <c r="M529" t="s" s="2">
-        <v>1469</v>
+        <v>1454</v>
       </c>
       <c r="N529" t="s" s="2">
-        <v>1470</v>
+        <v>1455</v>
       </c>
       <c r="O529" t="s" s="2">
-        <v>1471</v>
-      </c>
-      <c r="P529" s="2"/>
+        <v>1456</v>
+      </c>
+      <c r="P529" t="s" s="2">
+        <v>1457</v>
+      </c>
       <c r="Q529" t="s" s="2">
         <v>78</v>
       </c>
@@ -63057,13 +63122,13 @@
         <v>78</v>
       </c>
       <c r="Y529" t="s" s="2">
-        <v>78</v>
+        <v>517</v>
       </c>
       <c r="Z529" t="s" s="2">
-        <v>78</v>
+        <v>1458</v>
       </c>
       <c r="AA529" t="s" s="2">
-        <v>78</v>
+        <v>1459</v>
       </c>
       <c r="AB529" t="s" s="2">
         <v>78</v>
@@ -63081,7 +63146,7 @@
         <v>78</v>
       </c>
       <c r="AG529" t="s" s="2">
-        <v>1468</v>
+        <v>1453</v>
       </c>
       <c r="AH529" t="s" s="2">
         <v>76</v>
@@ -63098,13 +63163,13 @@
     </row>
     <row r="530">
       <c r="A530" t="s" s="2">
-        <v>1354</v>
+        <v>1371</v>
       </c>
       <c r="B530" t="s" s="2">
-        <v>1472</v>
+        <v>1460</v>
       </c>
       <c r="C530" t="s" s="2">
-        <v>1472</v>
+        <v>1460</v>
       </c>
       <c r="D530" s="2"/>
       <c r="E530" t="s" s="2">
@@ -63112,28 +63177,28 @@
       </c>
       <c r="F530" s="2"/>
       <c r="G530" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H530" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I530" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J530" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K530" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L530" t="s" s="2">
-        <v>1473</v>
+        <v>1461</v>
       </c>
       <c r="M530" t="s" s="2">
-        <v>1474</v>
+        <v>1462</v>
       </c>
       <c r="N530" t="s" s="2">
-        <v>1475</v>
+        <v>1463</v>
       </c>
       <c r="O530" s="2"/>
       <c r="P530" s="2"/>
@@ -63184,16 +63249,16 @@
         <v>78</v>
       </c>
       <c r="AG530" t="s" s="2">
-        <v>1472</v>
+        <v>1460</v>
       </c>
       <c r="AH530" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI530" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ530" t="s" s="2">
-        <v>78</v>
+        <v>1464</v>
       </c>
       <c r="AK530" t="s" s="2">
         <v>96</v>
@@ -63201,13 +63266,13 @@
     </row>
     <row r="531">
       <c r="A531" t="s" s="2">
-        <v>1476</v>
+        <v>1371</v>
       </c>
       <c r="B531" t="s" s="2">
-        <v>1476</v>
+        <v>1465</v>
       </c>
       <c r="C531" t="s" s="2">
-        <v>1476</v>
+        <v>1465</v>
       </c>
       <c r="D531" s="2"/>
       <c r="E531" t="s" s="2">
@@ -63218,7 +63283,7 @@
         <v>76</v>
       </c>
       <c r="H531" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I531" t="s" s="2">
         <v>78</v>
@@ -63230,13 +63295,13 @@
         <v>78</v>
       </c>
       <c r="L531" t="s" s="2">
-        <v>79</v>
+        <v>1466</v>
       </c>
       <c r="M531" t="s" s="2">
-        <v>1479</v>
+        <v>1467</v>
       </c>
       <c r="N531" t="s" s="2">
-        <v>1480</v>
+        <v>1468</v>
       </c>
       <c r="O531" s="2"/>
       <c r="P531" s="2"/>
@@ -63287,30 +63352,30 @@
         <v>78</v>
       </c>
       <c r="AG531" t="s" s="2">
-        <v>1237</v>
+        <v>1465</v>
       </c>
       <c r="AH531" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI531" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ531" t="s" s="2">
-        <v>78</v>
+        <v>1464</v>
       </c>
       <c r="AK531" t="s" s="2">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="s" s="2">
-        <v>1476</v>
+        <v>1371</v>
       </c>
       <c r="B532" t="s" s="2">
-        <v>1481</v>
+        <v>1469</v>
       </c>
       <c r="C532" t="s" s="2">
-        <v>1481</v>
+        <v>1469</v>
       </c>
       <c r="D532" s="2"/>
       <c r="E532" t="s" s="2">
@@ -63318,10 +63383,10 @@
       </c>
       <c r="F532" s="2"/>
       <c r="G532" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H532" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I532" t="s" s="2">
         <v>78</v>
@@ -63330,16 +63395,16 @@
         <v>78</v>
       </c>
       <c r="K532" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L532" t="s" s="2">
-        <v>86</v>
+        <v>383</v>
       </c>
       <c r="M532" t="s" s="2">
-        <v>1482</v>
+        <v>1470</v>
       </c>
       <c r="N532" t="s" s="2">
-        <v>1483</v>
+        <v>1471</v>
       </c>
       <c r="O532" s="2"/>
       <c r="P532" s="2"/>
@@ -63390,18 +63455,955 @@
         <v>78</v>
       </c>
       <c r="AG532" t="s" s="2">
+        <v>1469</v>
+      </c>
+      <c r="AH532" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI532" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ532" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK532" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="s" s="2">
+        <v>1371</v>
+      </c>
+      <c r="B533" t="s" s="2">
+        <v>1472</v>
+      </c>
+      <c r="C533" t="s" s="2">
+        <v>1472</v>
+      </c>
+      <c r="D533" s="2"/>
+      <c r="E533" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F533" s="2"/>
+      <c r="G533" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H533" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I533" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J533" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K533" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L533" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M533" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="N533" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="O533" s="2"/>
+      <c r="P533" s="2"/>
+      <c r="Q533" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R533" s="2"/>
+      <c r="S533" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T533" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U533" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V533" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W533" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X533" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y533" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z533" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA533" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB533" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC533" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD533" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE533" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF533" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG533" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AH533" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI533" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ533" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AK533" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="s" s="2">
+        <v>1371</v>
+      </c>
+      <c r="B534" t="s" s="2">
+        <v>1473</v>
+      </c>
+      <c r="C534" t="s" s="2">
+        <v>1473</v>
+      </c>
+      <c r="D534" s="2"/>
+      <c r="E534" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="F534" s="2"/>
+      <c r="G534" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H534" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I534" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J534" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K534" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L534" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="M534" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="N534" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O534" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="P534" s="2"/>
+      <c r="Q534" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R534" s="2"/>
+      <c r="S534" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T534" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U534" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V534" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W534" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X534" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y534" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z534" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA534" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB534" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC534" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD534" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE534" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF534" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG534" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AH534" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI534" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ534" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK534" t="s" s="2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="s" s="2">
+        <v>1371</v>
+      </c>
+      <c r="B535" t="s" s="2">
+        <v>1474</v>
+      </c>
+      <c r="C535" t="s" s="2">
+        <v>1474</v>
+      </c>
+      <c r="D535" s="2"/>
+      <c r="E535" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="F535" s="2"/>
+      <c r="G535" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H535" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I535" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J535" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K535" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L535" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="M535" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="N535" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="O535" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="P535" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="Q535" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R535" s="2"/>
+      <c r="S535" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T535" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U535" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V535" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W535" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X535" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y535" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z535" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA535" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB535" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC535" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD535" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE535" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF535" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG535" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AH535" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI535" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ535" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK535" t="s" s="2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="s" s="2">
+        <v>1371</v>
+      </c>
+      <c r="B536" t="s" s="2">
+        <v>1475</v>
+      </c>
+      <c r="C536" t="s" s="2">
+        <v>1475</v>
+      </c>
+      <c r="D536" s="2"/>
+      <c r="E536" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F536" s="2"/>
+      <c r="G536" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H536" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I536" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J536" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K536" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L536" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M536" t="s" s="2">
+        <v>1476</v>
+      </c>
+      <c r="N536" t="s" s="2">
+        <v>1477</v>
+      </c>
+      <c r="O536" s="2"/>
+      <c r="P536" s="2"/>
+      <c r="Q536" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R536" s="2"/>
+      <c r="S536" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T536" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U536" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V536" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W536" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X536" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y536" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="Z536" t="s" s="2">
+        <v>1478</v>
+      </c>
+      <c r="AA536" t="s" s="2">
+        <v>1479</v>
+      </c>
+      <c r="AB536" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC536" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD536" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE536" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF536" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG536" t="s" s="2">
+        <v>1475</v>
+      </c>
+      <c r="AH536" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI536" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ536" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK536" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="s" s="2">
+        <v>1371</v>
+      </c>
+      <c r="B537" t="s" s="2">
+        <v>1480</v>
+      </c>
+      <c r="C537" t="s" s="2">
+        <v>1480</v>
+      </c>
+      <c r="D537" s="2"/>
+      <c r="E537" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F537" s="2"/>
+      <c r="G537" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H537" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I537" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J537" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K537" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L537" t="s" s="2">
         <v>1481</v>
       </c>
-      <c r="AH532" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI532" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ532" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK532" t="s" s="2">
+      <c r="M537" t="s" s="2">
+        <v>1482</v>
+      </c>
+      <c r="N537" t="s" s="2">
+        <v>1483</v>
+      </c>
+      <c r="O537" t="s" s="2">
+        <v>1484</v>
+      </c>
+      <c r="P537" s="2"/>
+      <c r="Q537" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R537" s="2"/>
+      <c r="S537" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T537" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U537" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V537" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W537" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X537" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y537" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z537" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA537" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB537" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC537" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD537" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE537" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF537" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG537" t="s" s="2">
+        <v>1480</v>
+      </c>
+      <c r="AH537" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI537" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ537" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK537" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="s" s="2">
+        <v>1371</v>
+      </c>
+      <c r="B538" t="s" s="2">
+        <v>1485</v>
+      </c>
+      <c r="C538" t="s" s="2">
+        <v>1485</v>
+      </c>
+      <c r="D538" s="2"/>
+      <c r="E538" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F538" s="2"/>
+      <c r="G538" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H538" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I538" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J538" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K538" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L538" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="M538" t="s" s="2">
+        <v>1486</v>
+      </c>
+      <c r="N538" t="s" s="2">
+        <v>1487</v>
+      </c>
+      <c r="O538" t="s" s="2">
+        <v>1488</v>
+      </c>
+      <c r="P538" s="2"/>
+      <c r="Q538" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R538" s="2"/>
+      <c r="S538" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T538" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U538" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V538" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W538" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X538" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y538" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z538" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA538" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB538" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC538" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD538" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE538" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF538" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG538" t="s" s="2">
+        <v>1485</v>
+      </c>
+      <c r="AH538" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI538" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ538" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK538" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="s" s="2">
+        <v>1371</v>
+      </c>
+      <c r="B539" t="s" s="2">
+        <v>1489</v>
+      </c>
+      <c r="C539" t="s" s="2">
+        <v>1489</v>
+      </c>
+      <c r="D539" s="2"/>
+      <c r="E539" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F539" s="2"/>
+      <c r="G539" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H539" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I539" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J539" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K539" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L539" t="s" s="2">
+        <v>1490</v>
+      </c>
+      <c r="M539" t="s" s="2">
+        <v>1491</v>
+      </c>
+      <c r="N539" t="s" s="2">
+        <v>1492</v>
+      </c>
+      <c r="O539" s="2"/>
+      <c r="P539" s="2"/>
+      <c r="Q539" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R539" s="2"/>
+      <c r="S539" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T539" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U539" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V539" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W539" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X539" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y539" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z539" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA539" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB539" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC539" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD539" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE539" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF539" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG539" t="s" s="2">
+        <v>1489</v>
+      </c>
+      <c r="AH539" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI539" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ539" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK539" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="s" s="2">
+        <v>1493</v>
+      </c>
+      <c r="B540" t="s" s="2">
+        <v>1493</v>
+      </c>
+      <c r="C540" t="s" s="2">
+        <v>1493</v>
+      </c>
+      <c r="D540" s="2"/>
+      <c r="E540" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F540" s="2"/>
+      <c r="G540" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H540" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I540" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J540" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K540" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L540" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="M540" t="s" s="2">
+        <v>1496</v>
+      </c>
+      <c r="N540" t="s" s="2">
+        <v>1497</v>
+      </c>
+      <c r="O540" s="2"/>
+      <c r="P540" s="2"/>
+      <c r="Q540" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R540" s="2"/>
+      <c r="S540" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T540" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U540" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V540" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W540" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X540" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y540" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z540" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA540" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB540" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC540" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD540" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE540" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF540" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG540" t="s" s="2">
+        <v>1238</v>
+      </c>
+      <c r="AH540" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI540" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ540" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK540" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="s" s="2">
+        <v>1493</v>
+      </c>
+      <c r="B541" t="s" s="2">
+        <v>1498</v>
+      </c>
+      <c r="C541" t="s" s="2">
+        <v>1498</v>
+      </c>
+      <c r="D541" s="2"/>
+      <c r="E541" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F541" s="2"/>
+      <c r="G541" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H541" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I541" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J541" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K541" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L541" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="M541" t="s" s="2">
+        <v>1499</v>
+      </c>
+      <c r="N541" t="s" s="2">
+        <v>1500</v>
+      </c>
+      <c r="O541" s="2"/>
+      <c r="P541" s="2"/>
+      <c r="Q541" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R541" s="2"/>
+      <c r="S541" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T541" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U541" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V541" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W541" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X541" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y541" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z541" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA541" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB541" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC541" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD541" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE541" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF541" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG541" t="s" s="2">
+        <v>1498</v>
+      </c>
+      <c r="AH541" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI541" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ541" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK541" t="s" s="2">
         <v>78</v>
       </c>
     </row>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -1788,7 +1788,7 @@
     <t>Tillgängliggörande ändpunkt</t>
   </si>
   <si>
-    <t>2026-10-19T12:45:34+00:00</t>
+    <t>2026-10-19T13:06:20+00:00</t>
   </si>
   <si>
     <t>Den ändpunkt (TKEndpoint) som tillgängliggör denna API-instans ("tillgängliggör"). Basresursen CapabilityStatement har inget element för detta.</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -1788,7 +1788,7 @@
     <t>Tillgängliggörande ändpunkt</t>
   </si>
   <si>
-    <t>2026-10-19T13:06:20+00:00</t>
+    <t>2026-10-26T20:15:49+00:00</t>
   </si>
   <si>
     <t>Den ändpunkt (TKEndpoint) som tillgängliggör denna API-instans ("tillgängliggör"). Basresursen CapabilityStatement har inget element för detta.</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -1788,7 +1788,7 @@
     <t>Tillgängliggörande ändpunkt</t>
   </si>
   <si>
-    <t>2026-10-26T20:15:49+00:00</t>
+    <t>2026-10-26T20:25:02+00:00</t>
   </si>
   <si>
     <t>Den ändpunkt (TKEndpoint) som tillgängliggör denna API-instans ("tillgängliggör"). Basresursen CapabilityStatement har inget element för detta.</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -1835,7 +1835,7 @@
     <t>Tillgängliggörande ändpunkt</t>
   </si>
   <si>
-    <t>2026-10-27T17:54:53+00:00</t>
+    <t>2026-10-28T11:26:14+00:00</t>
   </si>
   <si>
     <t>Den ändpunkt (TKEndpoint) som tillgängliggör denna API-instans ("tillgängliggör"). Basresursen CapabilityStatement har inget element för detta.</t>
@@ -4029,11 +4029,11 @@
     <t>HSA-id (primär identifierare och logisk adress)</t>
   </si>
   <si>
-    <t>Organisationens HSA-id. Består av prefixet `SE`, organisationsnumret för den direktanslutna producenten i formatet tio siffror utan bindestreck, samt ett bindestreck och en efterföljande identifierande del. Organisationsnumret i HSA-id:t behöver inte vara organisationsnumret för den organisatoriska enhet som HSA-id:t identifierar. Värdet lagras, returneras och söks exakt som det är skrivet.</t>
+    <t>Organisationens HSA-id. Enligt HSA:s styrande dokument är ett HSA-id 1–31 tecken ur a–z, A–Z, 0–9 och bindestreck. Vanligen består det av `SE`, den direktanslutna producentens organisationsnummer utan bindestreck, ett bindestreck och en identifierande del (t.ex. `SE2321000016-1003`), men det finns undantag även i produktion. Ingenting får därför härledas ur ett HSA-id, inte heller ett organisationsnummer. Värdet lagras, returneras och söks exakt som det är skrivet.</t>
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-tk-org-hsaid-format:HSA-id består av SE, tio siffror (den direktanslutna producentens organisationsnummer utan bindestreck), ett bindestreck och en efterföljande identifierande del. {value.matches('^SE[0-9]{10}-.+$')}</t>
+tk-org-hsaid-format:HSA-id är 1–31 tecken ur a–z, A–Z, 0–9 och bindestreck, enligt HSA:s styrande dokument. {value.matches('^[a-zA-Z0-9-]{1,31}$')}</t>
   </si>
   <si>
     <t>Organization.identifier:hsaId.id</t>
